--- a/docs/xlsx/jobs-2026-10-20.xlsx
+++ b/docs/xlsx/jobs-2026-10-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="637">
   <si>
     <t>Title</t>
   </si>
@@ -40,18 +40,1254 @@
     <t>Link</t>
   </si>
   <si>
+    <t>2026 - AmeriCorps Member Positions Across Montana</t>
+  </si>
+  <si>
+    <t>Montana Fish, Wildlife &amp; Parks AmeriCorps</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$512 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2026---americorps-member-positions-across-montana-helena-montana/5528025217</t>
+  </si>
+  <si>
+    <t>Administrative Associate IV</t>
+  </si>
+  <si>
+    <t>Montana State University - Seed Potato Certification Program</t>
+  </si>
+  <si>
+    <t>Bozeman, MT</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$25.04 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-administrative-associate-iv-bozeman-montana/6787693855</t>
+  </si>
+  <si>
+    <t>Agricultural and Natural Resource Outreach Specialist</t>
+  </si>
+  <si>
+    <t>Sustainable Northwest</t>
+  </si>
+  <si>
+    <t>Burns, OR</t>
+  </si>
+  <si>
+    <t>$120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-agricultural-and-natural-resource-outreach-specialist-burns-oregon/3758336834</t>
+  </si>
+  <si>
+    <t>AmeriCorps Individual Placement – Engineering Technician</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Blairsville, GA</t>
+  </si>
+  <si>
+    <t>$945 per week</t>
+  </si>
+  <si>
+    <t>forestry-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-individual-placement--engineering-technician-blairsville-georgia/3881638973</t>
+  </si>
+  <si>
+    <t>Archivist (NPS, Aztec Ruins National Monument)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$30 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archivist-nps-aztec-ruins-national-monument-albuquerque-new-mexico/7520565322</t>
+  </si>
+  <si>
+    <t>Assistant Professor - Fisheries and Water Resources</t>
+  </si>
+  <si>
+    <t>University of Wisconsin - Stevens Point College of Natural Resources</t>
+  </si>
+  <si>
+    <t>Stevens Point, WI</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$65,000 - $72,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor---fisheries-and-water-resources-stevens-point-wisconsin/8012221352</t>
+  </si>
+  <si>
+    <t>BioCultural Forester</t>
+  </si>
+  <si>
+    <t>Forest Solutions Inc.</t>
+  </si>
+  <si>
+    <t>Keaau, HI</t>
+  </si>
+  <si>
+    <t>$60,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biocultural-forester-keaau-hawaii/6550610178</t>
+  </si>
+  <si>
+    <t>BRIDGE Program Coordinator</t>
+  </si>
+  <si>
+    <t>Smithsonian Environmental Research Center</t>
+  </si>
+  <si>
+    <t>Edgewater, MD</t>
+  </si>
+  <si>
+    <t>$70,623 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bridge-program-coordinator-edgewater-maryland/3483284164</t>
+  </si>
+  <si>
+    <t>Canvass Director</t>
+  </si>
+  <si>
+    <t>Fund for the Public Interest</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000-$53,750, depending on position and location.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-boston-massachusetts/2445485168</t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-minneapolis-minnesota/9443458861</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-philadelphia-pennsylvania/1442098889</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-portland-oregon/1638575699</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-chicago-illinois/5969155789</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Carolina - Individual Placement Program Coordinator</t>
+  </si>
+  <si>
+    <t>Conservation Legacy</t>
+  </si>
+  <si>
+    <t>Bahama, NC</t>
+  </si>
+  <si>
+    <t>$24.13 - $24.86 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps-north-carolina---individual-placement-program-coordinator-bahama-north-carolina/3852347206</t>
+  </si>
+  <si>
+    <t>Conservation Pilot- Okapi Wildlife Reserve.</t>
+  </si>
+  <si>
+    <t>Wild Conservation Society</t>
+  </si>
+  <si>
+    <t>Epulu, Africa</t>
+  </si>
+  <si>
+    <t>Competitive Salary commensurate with Experience</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-pilot--okapi-wildlife-reserve-epulu-africa/4593804637</t>
+  </si>
+  <si>
+    <t>Environmental Educator</t>
+  </si>
+  <si>
+    <t>Don Lee Center</t>
+  </si>
+  <si>
+    <t>Arapahoe, NC</t>
+  </si>
+  <si>
+    <t>$425 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-educator-arapahoe-north-carolina/3028349783</t>
+  </si>
+  <si>
+    <t>Environmental Program Educator</t>
+  </si>
+  <si>
+    <t>Solano Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Dixon, CA</t>
+  </si>
+  <si>
+    <t>$26.09 - $29.65 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-program-educator-dixon-california/3501777555</t>
+  </si>
+  <si>
+    <t>Executive and Development Coordinator</t>
+  </si>
+  <si>
+    <t>National Park Trust</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>$50,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-and-development-coordinator-rockville-maryland/5517096720</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>The Land Trust for Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>$33.65 - $40 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-assistant-santa-barbara-california/7860620851</t>
+  </si>
+  <si>
+    <t>Facilities and Maintenance Coordinator</t>
+  </si>
+  <si>
+    <t>Salmon Coast Society</t>
+  </si>
+  <si>
+    <t>Simoom Sound, Canada</t>
+  </si>
+  <si>
+    <t>$4,000 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facilities-and-maintenance-coordinator-simoom-sound-canada/3326083970</t>
+  </si>
+  <si>
+    <t>Field Logistics Technician</t>
+  </si>
+  <si>
+    <t>Utah Conservation Corps</t>
+  </si>
+  <si>
+    <t>Cedar City, Moab, or Logan, UT</t>
+  </si>
+  <si>
+    <t>$3,000 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-logistics-technician-cedar-city-moab-or-logan-utah/2480876681</t>
+  </si>
+  <si>
+    <t>Field Support Technician (ALL Programs)</t>
+  </si>
+  <si>
+    <t>Montana Conservation Corps</t>
+  </si>
+  <si>
+    <t>$2,880 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-support-technician-all-programs-bozeman-montana/4330582436</t>
+  </si>
+  <si>
+    <t>Forest Manager</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-manager-keaau-hawaii/9597865820</t>
+  </si>
+  <si>
+    <t>Forestry Specialist - Inspections (Municipal Arborist)</t>
+  </si>
+  <si>
+    <t>The Woodlands Township</t>
+  </si>
+  <si>
+    <t>The Woodlands, TX</t>
+  </si>
+  <si>
+    <t>$25.93 - $30 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-specialist---inspections-the-woodlands-texas/2397743420</t>
+  </si>
+  <si>
+    <t>General Counsel</t>
+  </si>
+  <si>
+    <t>American Rivers</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>$181,000 - $250,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-general-counsel-arlington-virginia/3271899558</t>
+  </si>
+  <si>
+    <t>Lead STEM Programs Educator</t>
+  </si>
+  <si>
+    <t>Mount Washington Observatory</t>
+  </si>
+  <si>
+    <t>North Conway, NH</t>
+  </si>
+  <si>
+    <t>$39,000 - $46,800 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lead-stem-programs-educator-north-conway-new-hampshire/5260868111</t>
+  </si>
+  <si>
+    <t>Postdoctoral Researcher in Wildlife Ecology at the Wildland-Urban Interface</t>
+  </si>
+  <si>
+    <t>University of California Santa Barbara</t>
+  </si>
+  <si>
+    <t>$71,491 - $85,736 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-researcher-in-wildlife-ecology-at-the-wildland-urban-interface-santa-barbara-california/8428936013</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Torch Conservation Center</t>
+  </si>
+  <si>
+    <t>Alden, MI</t>
+  </si>
+  <si>
+    <t>$30 - $35 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-manager-alden-michigan/1791141799</t>
+  </si>
+  <si>
+    <t>Regenerative Ranching Manager</t>
+  </si>
+  <si>
+    <t>Eastern, OR</t>
+  </si>
+  <si>
+    <t>$64,881 - $72,760 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regenerative-ranching-manager-eastern-oregon/5122752309</t>
+  </si>
+  <si>
+    <t>Research Administrative Assistant</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation for this position is $40,250-$42,750.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-administrative-assistant-denver-colorado/7356461091</t>
+  </si>
+  <si>
+    <t>Restoration Field Technician</t>
+  </si>
+  <si>
+    <t>Ojai Valley Land Conservancy</t>
+  </si>
+  <si>
+    <t>Ojai, CA</t>
+  </si>
+  <si>
+    <t>$25 - $27 per hour</t>
+  </si>
+  <si>
+    <t>botany-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-field-technician-ojai-california/4499710671</t>
+  </si>
+  <si>
+    <t>Restoration Site Operations Manager</t>
+  </si>
+  <si>
+    <t>GeoSystems Analysis Inc.</t>
+  </si>
+  <si>
+    <t>San Acacia, NM</t>
+  </si>
+  <si>
+    <t>$66,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-site-operations-manager-san-acacia-new-mexico/8169993892</t>
+  </si>
+  <si>
+    <t>Riverscapes Program Manager</t>
+  </si>
+  <si>
+    <t>Big Thompson Watershed Coalition</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>$68,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-riverscapes-program-manager-fort-collins-colorado/1627246007</t>
+  </si>
+  <si>
+    <t>STEM Programs Manager</t>
+  </si>
+  <si>
+    <t>$44,300 - $57,600 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stem-programs-manager-north-conway-new-hampshire/9443786544</t>
+  </si>
+  <si>
+    <t>Stormwater Maintenance Foreperson</t>
+  </si>
+  <si>
+    <t>EQR, LLC</t>
+  </si>
+  <si>
+    <t>Gambrills, MD</t>
+  </si>
+  <si>
+    <t>$25 - $31.75 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stormwater-maintenance-foreperson-gambrills-maryland/6278075573</t>
+  </si>
+  <si>
+    <t>Teacher/Naturalist</t>
+  </si>
+  <si>
+    <t>Echo Hill Outdoor School</t>
+  </si>
+  <si>
+    <t>Worton, MD</t>
+  </si>
+  <si>
+    <t>$350 - $400 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-teachernaturalist-worton-maryland/8798446759</t>
+  </si>
+  <si>
+    <t>Trail Crew Lead</t>
+  </si>
+  <si>
+    <t>Sitka Trail Works</t>
+  </si>
+  <si>
+    <t>Sitka, AK</t>
+  </si>
+  <si>
+    <t>$26 - $36 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trail-crew-lead-sitka-alaska/9433878746</t>
+  </si>
+  <si>
+    <t>Trail Strike Team Member</t>
+  </si>
+  <si>
+    <t>Wild South</t>
+  </si>
+  <si>
+    <t>Pisgah Forest, NC</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trail-strike-team-member-pisgah-forest-north-carolina/2464480542</t>
+  </si>
+  <si>
+    <t>USGS Ecological Statistics Research and Development</t>
+  </si>
+  <si>
+    <t>U.S. Department of the Interior (DOI)</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>Stipend $66,000.00 – $85,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usgs-ecological-statistics-research-and-development-bozeman-montana/9201404593</t>
+  </si>
+  <si>
+    <t>USGS Fire-Climate Adaptation Fellow</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Stipend $65,000.00 – $80,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usgs-fire-climate-adaptation-fellow-na-remote/5930327168</t>
+  </si>
+  <si>
+    <t>Vegetation Monitoring Seasonal Positions (GS 5-7)</t>
+  </si>
+  <si>
+    <t>National Park Service</t>
+  </si>
+  <si>
+    <t>Ashland, OR</t>
+  </si>
+  <si>
+    <t>$19.52 - $24.18 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vegetation-monitoring-seasonal-positions-gs-5-7-ashland-oregon/9139770063</t>
+  </si>
+  <si>
+    <t>Zero Waste Associate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-zero-waste-associate-los-angeles-california/9928324247</t>
+  </si>
+  <si>
+    <t>Technical Services Manager</t>
+  </si>
+  <si>
+    <t>Sequoia Ecological Consulting</t>
+  </si>
+  <si>
+    <t>California, United States, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/technical-services-manager/</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Oregon Jewish Community Foundation</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 24.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46eba3a58a99431dba532de60e5c45c1-administrative-assistant-oregon-jewish-community-foundation-portland</t>
+  </si>
+  <si>
+    <t>Wafa House, Inc.</t>
+  </si>
+  <si>
+    <t>Woodland Park, New Jersey</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Victim Support, Children Youth, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc0dd51d5b6242f78002f1b7468b1731-administrative-assistant-wafa-house-inc-woodland-park</t>
+  </si>
+  <si>
+    <t>Administrative Specialist - Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 30.92 - 40.13/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1846e534614749a7b242e804c5757fd4-administrative-specialist-personnel-and-human-resources-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Advancement Assistant</t>
+  </si>
+  <si>
+    <t>RICHMOND SYMPHONY</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 32000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df2a265b80bf4ac78d31d28c9f1a14ca-advancement-assistant-richmond-symphony-richmond</t>
+  </si>
+  <si>
+    <t>Assistant Controller</t>
+  </si>
+  <si>
+    <t>Way Finders, Inc.</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7699c5e6d9d641cdaa24c1e111983ace-assistant-controller-way-finders-inc-springfield</t>
+  </si>
+  <si>
+    <t>Associate Director of Youth Education</t>
+  </si>
+  <si>
+    <t>The Mountaineers</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 37.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9edfae21788f417b8573ddb23a1202b2-associate-director-of-youth-education-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Associate Director, Revenue Administration</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3932a452554c4a14bf3942fd083c61c8-associate-director-revenue-administration-animal-care-centers-of-nyc-bronx</t>
+  </si>
+  <si>
+    <t>Associate Professor/Professor of Practice in Counseling Psychology</t>
+  </si>
+  <si>
+    <t>The American University in Cairo</t>
+  </si>
+  <si>
+    <t>New Cairo City, Cairo Governorate, EG</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0d7891d0070a4121986f412ed3b23cee-associate-professorprofessor-of-practice-in-counseling-psychology-the-american-university-in-cairo-new-cairo-city</t>
+  </si>
+  <si>
+    <t>Business Systems Administrator</t>
+  </si>
+  <si>
+    <t>Energy Coordinating Agency</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efd68e872a00469ab329921f1afb568a-business-systems-administrator-energy-coordinating-agency-philadelphia</t>
+  </si>
+  <si>
+    <t>Campaign Manager</t>
+  </si>
+  <si>
+    <t>California Coastkeeper Alliance</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9330fc78f6d54c76ac480878f63dea6a-campaign-manager-california-coastkeeper-alliance-sacramento</t>
+  </si>
+  <si>
+    <t>Career Specialist</t>
+  </si>
+  <si>
+    <t>Youth Justice Network</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7ca05b9983e425d82c3a9d72bae40a2-career-specialist-youth-justice-network-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Nurse Manager</t>
+  </si>
+  <si>
+    <t>Iona Senior Services</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17a5108cca6f4a69b2985b5526ad91b2-clinical-nurse-manager-iona-senior-services-washington</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>WorkLife Law</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c0913eae0864dda9b6154a8efd60e22-communications-manager-worklife-law-san-francisco</t>
+  </si>
+  <si>
+    <t>Community Care Associate</t>
+  </si>
+  <si>
+    <t>Loudoun Hunger Relief</t>
+  </si>
+  <si>
+    <t>Sterling, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99e2fdd3f865496d9b50c6e4147af887-community-care-associate-loudoun-hunger-relief-sterling</t>
+  </si>
+  <si>
+    <t>Leesburg, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94ebbe582e134c2abfd999a7dc3fae17-community-care-associate-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>Community Education &amp; Outreach Manager</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48a325a80fef49f2a51313bd0d25193f-community-education-outreach-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Community Engagement Coordinator (Part-Time, Yonkers Outreach)</t>
+  </si>
+  <si>
+    <t>Environmental Leaders of Color</t>
+  </si>
+  <si>
+    <t>Yonkers, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76e46ea3bdb545a686ba959a0ce1ecc8-community-engagement-coordinator-part-time-yonkers-outreach-environmental-leaders-of-color-yonkers</t>
+  </si>
+  <si>
+    <t>Contacter para recaudación de fondos</t>
+  </si>
+  <si>
+    <t>Amnistía Internacional Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50fad245ea974004a55f3ab242b9a4ba-contacter-para-recaudacion-de-fondos-amnistia-internacional-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bf9daf271844a7eb7673065c55f288c-data-analyst-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Deaf Ministry Coordinator - Archdiocese of Washington</t>
+  </si>
+  <si>
+    <t>Archdiocese of Washington</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 83000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db7adcc7381d426492ba123a9a922513-deaf-ministry-coordinator-archdiocese-of-washington-archdiocese-of-washington-washington</t>
+  </si>
+  <si>
+    <t>Development and Operations Associate</t>
+  </si>
+  <si>
+    <t>Tookany/Tacony-Frankford Watershed Partnership, Inc.</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2467caf419c54a5da9fc0660302b07a1-development-and-operations-associate-tookanytacony-frankford-watershed-partnership-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b26d389520c44b96b006e16f3fd8837d-development-coordinator-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Ironbound Community Corporation of Newark, NJ</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2666caf7e5b64b19a370a07c59f72a5c-development-director-ironbound-community-corporation-of-newark-nj-newark</t>
+  </si>
+  <si>
+    <t>Pa'lante Transformative Justice</t>
+  </si>
+  <si>
+    <t>Holyoke, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a25fb38d66b7436eaef5738f6fb37128-development-director-palante-transformative-justice-holyoke</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Arcadia Center for Sustainable Food and Agriculture</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36a82832ba364c349f6e19a2093b68cb-development-manager-arcadia-center-for-sustainable-food-and-agriculture-alexandria</t>
+  </si>
+  <si>
+    <t>Digital Media Engineer</t>
+  </si>
+  <si>
+    <t>Trinity Church NYC</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc49beb282e14d86902a3bbdf5623e50-digital-media-engineer-trinity-church-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Birdhouse Neighborhood Center, Fourth &amp; Gill Neighborhood Organization</t>
+  </si>
+  <si>
+    <t>Knoxville, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebc280702db542759ff46b4363cd2f3b-director-birdhouse-neighborhood-center-fourth-gill-neighborhood-organization-knoxville</t>
+  </si>
+  <si>
+    <t>Director of Early Childhood Education</t>
+  </si>
+  <si>
+    <t>United South End Settlements</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/745b8660bd3a492796da4c9401237931-director-of-early-childhood-education-united-south-end-settlements-boston</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF LEGAL SERVICES</t>
+  </si>
+  <si>
+    <t>Catholic Migration Services</t>
+  </si>
+  <si>
+    <t>Remote (Queens County, New York)</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b45d53d1f664f5c9dfb4fbfe1a5c4da-director-of-legal-services-catholic-migration-services-queens-county</t>
+  </si>
+  <si>
+    <t>Director of Policy</t>
+  </si>
+  <si>
+    <t>UTEC</t>
+  </si>
+  <si>
+    <t>Lowell, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d864a3d34724ba38775e9963ca16ab4-director-of-policy-utec-lowell</t>
+  </si>
+  <si>
+    <t>Director of Political Affairs</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>USD 120676.00 - 134084.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b153a563ef04452ae3dca3ed16cbfd5-director-of-political-affairs-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Distribution Center &amp; Warehouse Associate- Full-Time and Part-Time Positions Available</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/873ed958acd245b996a08a29abb690ec-distribution-center-warehouse-associate-full-time-and-part-time-positions-available-loudoun-hunger-relief-sterling</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72ae987776fd4379ac49fbd43b3644c2-distribution-center-warehouse-associate-full-time-and-part-time-positions-available-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>Driver / Warehouse Associate</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43cd50c824784e6ea0122ce3be8a6439-driver-warehouse-associate-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3634cec95c254e7e9bc7acd867d4be4e-driver-warehouse-associate-loudoun-hunger-relief-sterling</t>
+  </si>
+  <si>
+    <t>Editor, Moldova</t>
+  </si>
+  <si>
+    <t>Organized Crime and Corruption Reporting Project</t>
+  </si>
+  <si>
+    <t>Remote (MD)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bfd7c7ea98c45ebbb5f769e129c83e9-editor-moldova-organized-crime-and-corruption-reporting-project-amsterdam</t>
+  </si>
+  <si>
+    <t>Education Programs Associate</t>
+  </si>
+  <si>
+    <t>NCPERS</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5da873ded9bf4880ba0fe86454b75580-education-programs-associate-ncpers-washington</t>
+  </si>
+  <si>
+    <t>Engineering Manager</t>
+  </si>
+  <si>
+    <t>First 5 Alameda County</t>
+  </si>
+  <si>
+    <t>Alameda, CA</t>
+  </si>
+  <si>
+    <t>USD 121000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a13d46e1dd5b4ff3b3e43beb39a7dccc-engineering-manager-first-5-alameda-county-alameda</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the Director &amp; CEO</t>
+  </si>
+  <si>
+    <t>The Newark Museum of Art</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bdbe7c7161c44ba85a947e34f7fb5be-executive-assistant-to-the-director-ceo-the-newark-museum-of-art-newark</t>
+  </si>
+  <si>
     <t>Executive Director - Local Corps Collective</t>
   </si>
   <si>
     <t>Los Angeles Conservation Corps</t>
   </si>
   <si>
-    <t>Los Angeles, CA</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 75.00 - 80.00/hour</t>
   </si>
   <si>
@@ -59,6 +1295,636 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/da881274d8704cdfb224592464ed1551-executive-director-local-corps-collective-los-angeles-conservation-corps-los-angeles</t>
+  </si>
+  <si>
+    <t>Executive Transformation and Strategy Officer</t>
+  </si>
+  <si>
+    <t>Heifer International</t>
+  </si>
+  <si>
+    <t>Agriculture, Poverty, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b06be3f8674847ec9a5eaf6b5522cd1b-executive-transformation-and-strategy-officer-heifer-international-little-rock</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e26a81bbc35d4c16af163a8ba5be70de-financial-analyst-utec-lowell</t>
+  </si>
+  <si>
+    <t>Founding Executive Director</t>
+  </si>
+  <si>
+    <t>The Fairfield Fund</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6c7bae243e74b30a76d96e6a4bb8863-founding-executive-director-the-fairfield-fund-verona</t>
+  </si>
+  <si>
+    <t>Grants and Contracts Analyst</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 83500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c1449f93f5a433893cfea249d788b94-grants-and-contracts-analyst-way-finders-inc-springfield</t>
+  </si>
+  <si>
+    <t>Housing Triage Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 83500.00 - 99500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f3672fdfb3049a89ec6905463e5ca6b-housing-triage-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>Cabrini Immigrant Services of NYC</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82bfeb70747f4833a739a31a939d1632-immigration-staff-attorney-cabrini-immigrant-services-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Legal Assistant/Screener</t>
+  </si>
+  <si>
+    <t>Pisgah Legal Services</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 46995.00 - 67696.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b61912c129274189a6194a74e4e41cc3-legal-assistantscreener-pisgah-legal-services-asheville</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Village Health Works</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6afc56df11c54e3783497959fb10bdf0-major-gifts-officer-village-health-works-new-york</t>
+  </si>
+  <si>
+    <t>Manager, School Partnerships</t>
+  </si>
+  <si>
+    <t>Jewish Federation of Greater Pittsburgh</t>
+  </si>
+  <si>
+    <t>Paramus, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28a02df9fa2849a7b45599f517f4d3e0-manager-school-partnerships-jewish-federation-of-greater-pittsburgh-paramus</t>
+  </si>
+  <si>
+    <t>Managing Director of External Affairs</t>
+  </si>
+  <si>
+    <t>OneGoal</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 119051.00 - 131656.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e5a2f3156854190a10a28a8fac623e5-managing-director-of-external-affairs-onegoal-chicago</t>
+  </si>
+  <si>
+    <t>Managing Family Law Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ecde76c9a5b496fbf8f3587d9d92e3e-managing-family-law-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Membership Assistant</t>
+  </si>
+  <si>
+    <t>Maryland State Education Association</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 53943.00 - 73652.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46e86203bd834c8580dcff2dc58da093-membership-assistant-maryland-state-education-association-annapolis</t>
+  </si>
+  <si>
+    <t>Membership Engagement Manager</t>
+  </si>
+  <si>
+    <t>American Academy of Arts and Sciences</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/281dd3714c6141a484a01c56b0a127b2-membership-engagement-manager-american-academy-of-arts-and-sciences-cambridge</t>
+  </si>
+  <si>
+    <t>Nutrition Program Manager</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0816237f20514b84a2f7211c9979ee80-nutrition-program-manager-iona-senior-services-washington</t>
+  </si>
+  <si>
+    <t>Part-time Accountant</t>
+  </si>
+  <si>
+    <t>LEV FOUNDATION</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e2a2c6acaf548d980177c79cccd3eb5-part-time-accountant-lev-foundation-seattle</t>
+  </si>
+  <si>
+    <t>Post-baccalaureate/Post-doctoral Bioethics Fellowship at the NIH</t>
+  </si>
+  <si>
+    <t>Department of Bioethics, Clinical Center, National Institutes of Health</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/28396133678a40698dab9f0f01737edf-post-baccalaureatepost-doctoral-bioethics-fellowship-at-the-nih-department-of-bioethics-clinical-center-national-institutes-of-health-bethesda</t>
+  </si>
+  <si>
+    <t>Preschool Teacher</t>
+  </si>
+  <si>
+    <t>Waterman's Community Center</t>
+  </si>
+  <si>
+    <t>North Haven, Maine</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/552dc6c810f54a4f9d87128b479af215-preschool-teacher-watermans-community-center-north-haven</t>
+  </si>
+  <si>
+    <t>Product Training &amp; Enablement Specialist</t>
+  </si>
+  <si>
+    <t>NAMI (National Alliance on Mental Illness)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/998e9695a41646eb8a3fd53cab604730-product-training-enablement-specialist-nami-national-alliance-on-mental-illness-arlington</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>New York Health Foundation</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Health Medicine, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be031c6e10ea434d9c07ac4b0903a306-program-assistant-new-york-health-foundation-new-york</t>
+  </si>
+  <si>
+    <t>PUBLIC DEFENDER CLIENT ADVOCATE</t>
+  </si>
+  <si>
+    <t>Partners for Justice</t>
+  </si>
+  <si>
+    <t>Chesterfield, Virginia</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 50605.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ddd04010d7e403698a036177ebe6d5e-public-defender-client-advocate-partners-for-justice-chesterfield</t>
+  </si>
+  <si>
+    <t>Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>Animal Aid Unlimited</t>
+  </si>
+  <si>
+    <t>Udaipur, RJ, IN</t>
+  </si>
+  <si>
+    <t>INR 20000.00 - 35000.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e600ad2895b4c9c9c9291e65530c30c-recruitment-specialist-animal-aid-unlimited-udaipur</t>
+  </si>
+  <si>
+    <t>Renter Attorney</t>
+  </si>
+  <si>
+    <t>Montana Legal Services Association</t>
+  </si>
+  <si>
+    <t>Helena, Montana</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee729955354745329b31aa4d2eccb3ae-renter-attorney-montana-legal-services-association-helena</t>
+  </si>
+  <si>
+    <t>Resiliency Specialist - Social Worker</t>
+  </si>
+  <si>
+    <t>Sanar Institute</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0ce1e05db9642f29305d55786b76b70-resiliency-specialist-social-worker-sanar-institute-newark</t>
+  </si>
+  <si>
+    <t>Senior Accountant, Accounts Payable &amp; Grants</t>
+  </si>
+  <si>
+    <t>Jewish Federation Bay Area</t>
+  </si>
+  <si>
+    <t>USD 91000.00 - 107000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1efbee1b1a274bc8b03ef42f6e1ae9cd-senior-accountant-accounts-payable-grants-jewish-federation-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Civil Litigation Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b4d55f22fd6471585ac588baf948f61-senior-civil-litigation-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Eviction Defense (UD) Housing Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2f9b62febb74f6fa0e216a945a0b084-senior-eviction-defense-ud-housing-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Officer, Learning &amp; Impact</t>
+  </si>
+  <si>
+    <t>Equality Fund</t>
+  </si>
+  <si>
+    <t>Remote (CA)</t>
+  </si>
+  <si>
+    <t>CAD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Microfinance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c96ab29aa79d4972ad178891bcc0a9e8-senior-officer-learning-impact-equality-fund-ottawa</t>
+  </si>
+  <si>
+    <t>Senior Probate Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0ce69030b574787b92b120f28ea2f06-senior-probate-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Strategist, Federal Advocacy, Advocacy &amp; Partnerships</t>
+  </si>
+  <si>
+    <t>Vera Institute of Justice</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Immigrants Or Refugees, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ef7896729154f5192c24223ce04c86c-senior-strategist-federal-advocacy-advocacy-partnerships-vera-institute-of-justice-washington</t>
+  </si>
+  <si>
+    <t>Service Coordinator for Montgomery County</t>
+  </si>
+  <si>
+    <t>The Choice Program at UMBC</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 50500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Prison Reform, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c83dd18b5034411afc1ec79d6605982-service-coordinator-for-montgomery-county-the-choice-program-at-umbc-hyattsville</t>
+  </si>
+  <si>
+    <t>Special Assistant</t>
+  </si>
+  <si>
+    <t>Guardrails Action</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c603a74fb4d848e8903de4dcfb4ee054-special-assistant-guardrails-action-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5704bf4031554c78a75bef4226c81200-special-assistant-guardrails-action-washington</t>
+  </si>
+  <si>
+    <t>Specialist, Institutional Partnerships</t>
+  </si>
+  <si>
+    <t>Capital Area Food Bank</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 27.29 - 33.35/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Hunger Food Security, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5cdf9881d47841b2aa4fda58484ad5a0-specialist-institutional-partnerships-capital-area-food-bank-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant I</t>
+  </si>
+  <si>
+    <t>USD 28.85 - 28.85/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/848e599d588e44aeb86a3ebdc5fea4ea-staff-accountant-i-utec-lowell</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Coalition to Abolish Slavery &amp; Trafficking (CAST)</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4875e1d033f48e8b4ee3fe3d74e8873-staff-attorney-coalition-to-abolish-slavery-trafficking-cast-los-angeles</t>
+  </si>
+  <si>
+    <t>Housing Conservation Coordinators, Inc.</t>
+  </si>
+  <si>
+    <t>USD 80841.00 - 134389.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d308f504ded44a3ae62810e5ff8d53e-staff-attorney-housing-conservation-coordinators-inc-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Tenant Advocacy Program</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 79393.12 - 89846.66/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e362f846f1f546008b3bc8f0542999c0-staff-attorney-tenant-advocacy-program-catholic-migration-services-queens-county</t>
+  </si>
+  <si>
+    <t>Substance Use Treatment and Education Coordinator (PSH)</t>
+  </si>
+  <si>
+    <t>Delivering Innovation in Supportive Housing (DISH)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efd9bf2d412b4aae9a1cc338948d71f8-substance-use-treatment-and-education-coordinator-psh-delivering-innovation-in-supportive-housing-dish-san-francisco</t>
+  </si>
+  <si>
+    <t>Supervising or Staff Attorney, Women &amp; Survivors Program</t>
+  </si>
+  <si>
+    <t>Illinois Prison Project</t>
+  </si>
+  <si>
+    <t>USD 100059.00 - 130080.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Prison Reform, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/757740555ee146b9ab78c72769a082b5-supervising-or-staff-attorney-women-survivors-program-illinois-prison-project-chicago</t>
+  </si>
+  <si>
+    <t>Tech Lead — Backend &amp; Platform</t>
+  </si>
+  <si>
+    <t>Basta</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67975dc08cc54571bd508859eca3df46-tech-lead-backend-platform-basta-new-york</t>
+  </si>
+  <si>
+    <t>Technical Advisor – International Business &amp; Economic Development</t>
+  </si>
+  <si>
+    <t>USD 97038.00 - 126024.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/685c9565cfa34a16bb9f1e189115d2eb-technical-advisor-international-business-economic-development-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Technology Operations Director</t>
+  </si>
+  <si>
+    <t>Resources Legacy Fund</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/124a3f8c39cb4a8280cf58c9da02f4c8-technology-operations-director-resources-legacy-fund-sacramento</t>
+  </si>
+  <si>
+    <t>Temporary Affirmative Housing Paralegal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c90bb16f87a47d2bc6ffc4d6ca16a97-temporary-affirmative-housing-paralegal-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Temporary Probate Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a07325006e745eb9d12074d70318a9d-temporary-probate-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Toddler/Preschool Teacher</t>
+  </si>
+  <si>
+    <t>USD 48500.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b2e06426ad5405da61bd84f0b4b2fba-toddlerpreschool-teacher-utec-lowell</t>
+  </si>
+  <si>
+    <t>Victim Services Coordinator</t>
+  </si>
+  <si>
+    <t>Victim Support Services</t>
+  </si>
+  <si>
+    <t>Everett, WA</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Men</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d82a2ff7f2814bfaa44ba5430b5820ce-victim-services-coordinator-victim-support-services-everett</t>
+  </si>
+  <si>
+    <t>Web Developer &amp; Digital Applications Specialist</t>
+  </si>
+  <si>
+    <t>Baltimore Museum of Art</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 38.98 - 38.98/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f95075c2e1ba436894ba18eb12b040e9-web-developer-digital-applications-specialist-baltimore-museum-of-art-baltimore</t>
+  </si>
+  <si>
+    <t>Youth Programming Manager</t>
+  </si>
+  <si>
+    <t>S.A.V.E.</t>
+  </si>
+  <si>
+    <t>Hollywood, Florida</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b94a9249d9c4eb8886838d0e12a7987-youth-programming-manager-save-hollywood</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,62 +2349,1024 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>179</v>
+      </c>
+      <c r="B35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" t="s">
+        <v>177</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" t="s">
+        <v>198</v>
+      </c>
+      <c r="C39" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>200</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E40" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" t="s">
+        <v>206</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" t="s">
+        <v>209</v>
+      </c>
+      <c r="D41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" t="s">
+        <v>217</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43" t="s">
+        <v>223</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -581,31 +3409,2193 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>227</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>229</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H89"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" t="s">
+        <v>279</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F11" t="s">
+        <v>290</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" t="s">
+        <v>296</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" t="s">
+        <v>302</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" t="s">
+        <v>301</v>
+      </c>
+      <c r="F14" t="s">
+        <v>307</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" t="s">
+        <v>313</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" t="s">
+        <v>313</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>318</v>
+      </c>
+      <c r="C17" t="s">
+        <v>319</v>
+      </c>
+      <c r="D17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F17" t="s">
+        <v>321</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" t="s">
+        <v>324</v>
+      </c>
+      <c r="C18" t="s">
+        <v>325</v>
+      </c>
+      <c r="D18" t="s">
+        <v>326</v>
+      </c>
+      <c r="E18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" t="s">
+        <v>328</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" t="s">
+        <v>332</v>
+      </c>
+      <c r="D19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B20" t="s">
+        <v>335</v>
+      </c>
+      <c r="C20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>337</v>
+      </c>
+      <c r="B21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F21" t="s">
+        <v>340</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>342</v>
+      </c>
+      <c r="B22" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" t="s">
+        <v>345</v>
+      </c>
+      <c r="F22" t="s">
+        <v>346</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" t="s">
+        <v>312</v>
+      </c>
+      <c r="F23" t="s">
+        <v>313</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B24" t="s">
+        <v>351</v>
+      </c>
+      <c r="C24" t="s">
+        <v>352</v>
+      </c>
+      <c r="D24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" t="s">
+        <v>353</v>
+      </c>
+      <c r="F24" t="s">
+        <v>328</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25" t="s">
+        <v>357</v>
+      </c>
+      <c r="F25" t="s">
+        <v>358</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>360</v>
+      </c>
+      <c r="B26" t="s">
+        <v>361</v>
+      </c>
+      <c r="C26" t="s">
+        <v>247</v>
+      </c>
+      <c r="D26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" t="s">
+        <v>363</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" t="s">
+        <v>366</v>
+      </c>
+      <c r="C27" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" t="s">
+        <v>278</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" t="s">
+        <v>370</v>
+      </c>
+      <c r="C28" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
+        <v>372</v>
+      </c>
+      <c r="F28" t="s">
+        <v>373</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B29" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" t="s">
+        <v>377</v>
+      </c>
+      <c r="F29" t="s">
+        <v>296</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B30" t="s">
+        <v>380</v>
+      </c>
+      <c r="C30" t="s">
+        <v>381</v>
+      </c>
+      <c r="D30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" t="s">
+        <v>382</v>
+      </c>
+      <c r="F30" t="s">
+        <v>383</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B31" t="s">
+        <v>386</v>
+      </c>
+      <c r="C31" t="s">
+        <v>387</v>
+      </c>
+      <c r="D31" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" t="s">
+        <v>388</v>
+      </c>
+      <c r="F31" t="s">
+        <v>389</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>391</v>
+      </c>
+      <c r="B32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>393</v>
+      </c>
+      <c r="F32" t="s">
+        <v>278</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" t="s">
+        <v>310</v>
+      </c>
+      <c r="C33" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" t="s">
+        <v>396</v>
+      </c>
+      <c r="F33" t="s">
+        <v>313</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>395</v>
+      </c>
+      <c r="B34" t="s">
+        <v>310</v>
+      </c>
+      <c r="C34" t="s">
+        <v>315</v>
+      </c>
+      <c r="D34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F34" t="s">
+        <v>313</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>399</v>
+      </c>
+      <c r="B35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C35" t="s">
+        <v>315</v>
+      </c>
+      <c r="D35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" t="s">
+        <v>400</v>
+      </c>
+      <c r="F35" t="s">
+        <v>313</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>399</v>
+      </c>
+      <c r="B36" t="s">
+        <v>310</v>
+      </c>
+      <c r="C36" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" t="s">
+        <v>400</v>
+      </c>
+      <c r="F36" t="s">
+        <v>313</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>403</v>
+      </c>
+      <c r="B37" t="s">
+        <v>404</v>
+      </c>
+      <c r="C37" t="s">
+        <v>405</v>
+      </c>
+      <c r="D37" t="s">
+        <v>406</v>
+      </c>
+      <c r="E37" t="s">
+        <v>278</v>
+      </c>
+      <c r="F37" t="s">
+        <v>278</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>408</v>
+      </c>
+      <c r="B38" t="s">
+        <v>409</v>
+      </c>
+      <c r="C38" t="s">
+        <v>300</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" t="s">
+        <v>410</v>
+      </c>
+      <c r="F38" t="s">
+        <v>411</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>413</v>
+      </c>
+      <c r="B39" t="s">
+        <v>414</v>
+      </c>
+      <c r="C39" t="s">
+        <v>415</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>416</v>
+      </c>
+      <c r="F39" t="s">
+        <v>417</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40" t="s">
+        <v>420</v>
+      </c>
+      <c r="C40" t="s">
+        <v>352</v>
+      </c>
+      <c r="D40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" t="s">
+        <v>357</v>
+      </c>
+      <c r="F40" t="s">
+        <v>255</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>422</v>
+      </c>
+      <c r="B41" t="s">
+        <v>423</v>
+      </c>
+      <c r="C41" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" t="s">
+        <v>406</v>
+      </c>
+      <c r="E41" t="s">
+        <v>424</v>
+      </c>
+      <c r="F41" t="s">
+        <v>425</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>427</v>
+      </c>
+      <c r="B42" t="s">
+        <v>428</v>
+      </c>
+      <c r="C42" t="s">
+        <v>306</v>
+      </c>
+      <c r="D42" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" t="s">
+        <v>278</v>
+      </c>
+      <c r="F42" t="s">
+        <v>429</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>431</v>
+      </c>
+      <c r="B43" t="s">
+        <v>386</v>
+      </c>
+      <c r="C43" t="s">
+        <v>387</v>
+      </c>
+      <c r="D43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" t="s">
+        <v>432</v>
+      </c>
+      <c r="F43" t="s">
+        <v>389</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>434</v>
+      </c>
+      <c r="B44" t="s">
+        <v>435</v>
+      </c>
+      <c r="C44" t="s">
+        <v>306</v>
+      </c>
+      <c r="D44" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44" t="s">
+        <v>436</v>
+      </c>
+      <c r="F44" t="s">
+        <v>437</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>439</v>
+      </c>
+      <c r="B45" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" t="s">
+        <v>259</v>
+      </c>
+      <c r="D45" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F45" t="s">
+        <v>261</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>442</v>
+      </c>
+      <c r="B46" t="s">
+        <v>443</v>
+      </c>
+      <c r="C46" t="s">
+        <v>444</v>
+      </c>
+      <c r="D46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46" t="s">
+        <v>445</v>
+      </c>
+      <c r="F46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>447</v>
+      </c>
+      <c r="B47" t="s">
+        <v>448</v>
+      </c>
+      <c r="C47" t="s">
+        <v>294</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F47" t="s">
+        <v>278</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>451</v>
+      </c>
+      <c r="B48" t="s">
+        <v>452</v>
+      </c>
+      <c r="C48" t="s">
+        <v>453</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" t="s">
+        <v>454</v>
+      </c>
+      <c r="F48" t="s">
+        <v>278</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>456</v>
+      </c>
+      <c r="B49" t="s">
+        <v>457</v>
+      </c>
+      <c r="C49" t="s">
+        <v>458</v>
+      </c>
+      <c r="D49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" t="s">
+        <v>301</v>
+      </c>
+      <c r="F49" t="s">
+        <v>459</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>461</v>
+      </c>
+      <c r="B50" t="s">
+        <v>462</v>
+      </c>
+      <c r="C50" t="s">
+        <v>463</v>
+      </c>
+      <c r="D50" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" t="s">
+        <v>464</v>
+      </c>
+      <c r="F50" t="s">
+        <v>465</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>467</v>
+      </c>
+      <c r="B51" t="s">
+        <v>468</v>
+      </c>
+      <c r="C51" t="s">
+        <v>469</v>
+      </c>
+      <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" t="s">
+        <v>470</v>
+      </c>
+      <c r="F51" t="s">
+        <v>471</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>473</v>
+      </c>
+      <c r="B52" t="s">
+        <v>443</v>
+      </c>
+      <c r="C52" t="s">
+        <v>444</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" t="s">
+        <v>278</v>
+      </c>
+      <c r="F52" t="s">
+        <v>278</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>475</v>
+      </c>
+      <c r="B53" t="s">
+        <v>476</v>
+      </c>
+      <c r="C53" t="s">
+        <v>477</v>
+      </c>
+      <c r="D53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E53" t="s">
+        <v>478</v>
+      </c>
+      <c r="F53" t="s">
+        <v>479</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>481</v>
+      </c>
+      <c r="B54" t="s">
+        <v>482</v>
+      </c>
+      <c r="C54" t="s">
+        <v>483</v>
+      </c>
+      <c r="D54" t="s">
+        <v>241</v>
+      </c>
+      <c r="E54" t="s">
+        <v>484</v>
+      </c>
+      <c r="F54" t="s">
+        <v>485</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>487</v>
+      </c>
+      <c r="B55" t="s">
+        <v>299</v>
+      </c>
+      <c r="C55" t="s">
+        <v>300</v>
+      </c>
+      <c r="D55" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" t="s">
+        <v>488</v>
+      </c>
+      <c r="F55" t="s">
+        <v>489</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>491</v>
+      </c>
+      <c r="B56" t="s">
+        <v>492</v>
+      </c>
+      <c r="C56" t="s">
+        <v>493</v>
+      </c>
+      <c r="D56" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" t="s">
+        <v>312</v>
+      </c>
+      <c r="F56" t="s">
+        <v>471</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>495</v>
+      </c>
+      <c r="B57" t="s">
+        <v>496</v>
+      </c>
+      <c r="C57" t="s">
+        <v>497</v>
+      </c>
+      <c r="D57" t="s">
+        <v>288</v>
+      </c>
+      <c r="E57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F57" t="s">
+        <v>498</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>500</v>
+      </c>
+      <c r="B58" t="s">
+        <v>501</v>
+      </c>
+      <c r="C58" t="s">
+        <v>502</v>
+      </c>
+      <c r="D58" t="s">
+        <v>241</v>
+      </c>
+      <c r="E58" t="s">
+        <v>503</v>
+      </c>
+      <c r="F58" t="s">
+        <v>504</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>506</v>
+      </c>
+      <c r="B59" t="s">
+        <v>507</v>
+      </c>
+      <c r="C59" t="s">
+        <v>306</v>
+      </c>
+      <c r="D59" t="s">
+        <v>241</v>
+      </c>
+      <c r="E59" t="s">
+        <v>508</v>
+      </c>
+      <c r="F59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>511</v>
+      </c>
+      <c r="B60" t="s">
+        <v>512</v>
+      </c>
+      <c r="C60" t="s">
+        <v>294</v>
+      </c>
+      <c r="D60" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" t="s">
+        <v>513</v>
+      </c>
+      <c r="F60" t="s">
+        <v>514</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>516</v>
+      </c>
+      <c r="B61" t="s">
+        <v>517</v>
+      </c>
+      <c r="C61" t="s">
+        <v>518</v>
+      </c>
+      <c r="D61" t="s">
+        <v>241</v>
+      </c>
+      <c r="E61" t="s">
+        <v>519</v>
+      </c>
+      <c r="F61" t="s">
+        <v>520</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>522</v>
+      </c>
+      <c r="B62" t="s">
+        <v>523</v>
+      </c>
+      <c r="C62" t="s">
+        <v>524</v>
+      </c>
+      <c r="D62" t="s">
+        <v>241</v>
+      </c>
+      <c r="E62" t="s">
+        <v>525</v>
+      </c>
+      <c r="F62" t="s">
+        <v>526</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>528</v>
+      </c>
+      <c r="B63" t="s">
+        <v>529</v>
+      </c>
+      <c r="C63" t="s">
+        <v>530</v>
+      </c>
+      <c r="D63" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" t="s">
+        <v>531</v>
+      </c>
+      <c r="F63" t="s">
+        <v>532</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>534</v>
+      </c>
+      <c r="B64" t="s">
+        <v>535</v>
+      </c>
+      <c r="C64" t="s">
+        <v>352</v>
+      </c>
+      <c r="D64" t="s">
+        <v>241</v>
+      </c>
+      <c r="E64" t="s">
+        <v>320</v>
+      </c>
+      <c r="F64" t="s">
+        <v>536</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>538</v>
+      </c>
+      <c r="B65" t="s">
+        <v>539</v>
+      </c>
+      <c r="C65" t="s">
+        <v>444</v>
+      </c>
+      <c r="D65" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" t="s">
+        <v>540</v>
+      </c>
+      <c r="F65" t="s">
+        <v>237</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>542</v>
+      </c>
+      <c r="B66" t="s">
+        <v>443</v>
+      </c>
+      <c r="C66" t="s">
+        <v>444</v>
+      </c>
+      <c r="D66" t="s">
+        <v>241</v>
+      </c>
+      <c r="E66" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" t="s">
+        <v>278</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>544</v>
+      </c>
+      <c r="B67" t="s">
+        <v>443</v>
+      </c>
+      <c r="C67" t="s">
+        <v>444</v>
+      </c>
+      <c r="D67" t="s">
+        <v>241</v>
+      </c>
+      <c r="E67" t="s">
+        <v>278</v>
+      </c>
+      <c r="F67" t="s">
+        <v>278</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>546</v>
+      </c>
+      <c r="B68" t="s">
+        <v>547</v>
+      </c>
+      <c r="C68" t="s">
+        <v>548</v>
+      </c>
+      <c r="D68" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" t="s">
+        <v>549</v>
+      </c>
+      <c r="F68" t="s">
+        <v>550</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>552</v>
+      </c>
+      <c r="B69" t="s">
+        <v>443</v>
+      </c>
+      <c r="C69" t="s">
+        <v>444</v>
+      </c>
+      <c r="D69" t="s">
+        <v>241</v>
+      </c>
+      <c r="E69" t="s">
+        <v>278</v>
+      </c>
+      <c r="F69" t="s">
+        <v>278</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>554</v>
+      </c>
+      <c r="B70" t="s">
+        <v>555</v>
+      </c>
+      <c r="C70" t="s">
+        <v>300</v>
+      </c>
+      <c r="D70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E70" t="s">
+        <v>556</v>
+      </c>
+      <c r="F70" t="s">
+        <v>557</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>559</v>
+      </c>
+      <c r="B71" t="s">
+        <v>560</v>
+      </c>
+      <c r="C71" t="s">
+        <v>561</v>
+      </c>
+      <c r="D71" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" t="s">
+        <v>562</v>
+      </c>
+      <c r="F71" t="s">
+        <v>563</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>565</v>
+      </c>
+      <c r="B72" t="s">
+        <v>566</v>
+      </c>
+      <c r="C72" t="s">
+        <v>306</v>
+      </c>
+      <c r="D72" t="s">
+        <v>241</v>
+      </c>
+      <c r="E72" t="s">
+        <v>260</v>
+      </c>
+      <c r="F72" t="s">
+        <v>278</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>565</v>
+      </c>
+      <c r="B73" t="s">
+        <v>566</v>
+      </c>
+      <c r="C73" t="s">
+        <v>306</v>
+      </c>
+      <c r="D73" t="s">
+        <v>241</v>
+      </c>
+      <c r="E73" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73" t="s">
+        <v>278</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>569</v>
+      </c>
+      <c r="B74" t="s">
+        <v>570</v>
+      </c>
+      <c r="C74" t="s">
+        <v>571</v>
+      </c>
+      <c r="D74" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74" t="s">
+        <v>572</v>
+      </c>
+      <c r="F74" t="s">
+        <v>573</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>575</v>
+      </c>
+      <c r="B75" t="s">
+        <v>386</v>
+      </c>
+      <c r="C75" t="s">
+        <v>387</v>
+      </c>
+      <c r="D75" t="s">
+        <v>235</v>
+      </c>
+      <c r="E75" t="s">
+        <v>576</v>
+      </c>
+      <c r="F75" t="s">
+        <v>577</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>579</v>
+      </c>
+      <c r="B76" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" t="s">
+        <v>581</v>
+      </c>
+      <c r="D76" t="s">
+        <v>241</v>
+      </c>
+      <c r="E76" t="s">
+        <v>582</v>
+      </c>
+      <c r="F76" t="s">
+        <v>278</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>579</v>
+      </c>
+      <c r="B77" t="s">
+        <v>584</v>
+      </c>
+      <c r="C77" t="s">
+        <v>294</v>
+      </c>
+      <c r="D77" t="s">
+        <v>241</v>
+      </c>
+      <c r="E77" t="s">
+        <v>585</v>
+      </c>
+      <c r="F77" t="s">
+        <v>586</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>588</v>
+      </c>
+      <c r="B78" t="s">
+        <v>380</v>
+      </c>
+      <c r="C78" t="s">
+        <v>589</v>
+      </c>
+      <c r="D78" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78" t="s">
+        <v>590</v>
+      </c>
+      <c r="F78" t="s">
+        <v>383</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>592</v>
+      </c>
+      <c r="B79" t="s">
+        <v>593</v>
+      </c>
+      <c r="C79" t="s">
+        <v>444</v>
+      </c>
+      <c r="D79" t="s">
+        <v>288</v>
+      </c>
+      <c r="E79" t="s">
+        <v>594</v>
+      </c>
+      <c r="F79" t="s">
+        <v>595</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>597</v>
+      </c>
+      <c r="B80" t="s">
+        <v>598</v>
+      </c>
+      <c r="C80" t="s">
+        <v>469</v>
+      </c>
+      <c r="D80" t="s">
+        <v>241</v>
+      </c>
+      <c r="E80" t="s">
+        <v>599</v>
+      </c>
+      <c r="F80" t="s">
+        <v>600</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>602</v>
+      </c>
+      <c r="B81" t="s">
+        <v>603</v>
+      </c>
+      <c r="C81" t="s">
+        <v>306</v>
+      </c>
+      <c r="D81" t="s">
+        <v>241</v>
+      </c>
+      <c r="E81" t="s">
+        <v>604</v>
+      </c>
+      <c r="F81" t="s">
+        <v>279</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>606</v>
+      </c>
+      <c r="B82" t="s">
+        <v>246</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" t="s">
+        <v>241</v>
+      </c>
+      <c r="E82" t="s">
+        <v>607</v>
+      </c>
+      <c r="F82" t="s">
+        <v>249</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>609</v>
+      </c>
+      <c r="B83" t="s">
+        <v>610</v>
+      </c>
+      <c r="C83" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" t="s">
+        <v>241</v>
+      </c>
+      <c r="E83" t="s">
+        <v>611</v>
+      </c>
+      <c r="F83" t="s">
+        <v>612</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>614</v>
+      </c>
+      <c r="B84" t="s">
+        <v>443</v>
+      </c>
+      <c r="C84" t="s">
+        <v>444</v>
+      </c>
+      <c r="D84" t="s">
+        <v>241</v>
+      </c>
+      <c r="E84" t="s">
+        <v>278</v>
+      </c>
+      <c r="F84" t="s">
+        <v>278</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>616</v>
+      </c>
+      <c r="B85" t="s">
+        <v>443</v>
+      </c>
+      <c r="C85" t="s">
+        <v>444</v>
+      </c>
+      <c r="D85" t="s">
+        <v>241</v>
+      </c>
+      <c r="E85" t="s">
+        <v>278</v>
+      </c>
+      <c r="F85" t="s">
+        <v>278</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>618</v>
+      </c>
+      <c r="B86" t="s">
+        <v>386</v>
+      </c>
+      <c r="C86" t="s">
+        <v>387</v>
+      </c>
+      <c r="D86" t="s">
+        <v>241</v>
+      </c>
+      <c r="E86" t="s">
+        <v>619</v>
+      </c>
+      <c r="F86" t="s">
+        <v>577</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>621</v>
+      </c>
+      <c r="B87" t="s">
+        <v>622</v>
+      </c>
+      <c r="C87" t="s">
+        <v>623</v>
+      </c>
+      <c r="D87" t="s">
+        <v>288</v>
+      </c>
+      <c r="E87" t="s">
+        <v>624</v>
+      </c>
+      <c r="F87" t="s">
+        <v>625</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>627</v>
+      </c>
+      <c r="B88" t="s">
+        <v>628</v>
+      </c>
+      <c r="C88" t="s">
+        <v>629</v>
+      </c>
+      <c r="D88" t="s">
+        <v>235</v>
+      </c>
+      <c r="E88" t="s">
+        <v>630</v>
+      </c>
+      <c r="F88" t="s">
+        <v>504</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>632</v>
+      </c>
+      <c r="B89" t="s">
+        <v>633</v>
+      </c>
+      <c r="C89" t="s">
+        <v>634</v>
+      </c>
+      <c r="D89" t="s">
+        <v>241</v>
+      </c>
+      <c r="E89" t="s">
+        <v>513</v>
+      </c>
+      <c r="F89" t="s">
+        <v>635</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-20.xlsx
+++ b/docs/xlsx/jobs-2026-10-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="849">
   <si>
     <t>Title</t>
   </si>
@@ -382,6 +382,9 @@
     <t>admin-leadership-general-stewardship</t>
   </si>
   <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
     <t>https://www.conservationjobboard.com/job-listing-field-support-technician-all-programs-bozeman-montana/4330582436</t>
   </si>
   <si>
@@ -691,6 +694,39 @@
     <t>https://www.conservationjobboard.com/job-listing-zero-waste-associate-los-angeles-california/9928324247</t>
   </si>
   <si>
+    <t>Field Organizer</t>
+  </si>
+  <si>
+    <t>Sierra Watch</t>
+  </si>
+  <si>
+    <t>Truckee, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/field-organizer-3/</t>
+  </si>
+  <si>
+    <t>Montana, United States, United States</t>
+  </si>
+  <si>
+    <t>Less than 20,000</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/field-support-technician-all-programs/</t>
+  </si>
+  <si>
     <t>Technical Services Manager</t>
   </si>
   <si>
@@ -700,18 +736,33 @@
     <t>California, United States, United States</t>
   </si>
   <si>
-    <t>Full-Time</t>
-  </si>
-  <si>
     <t>100,000 and above</t>
   </si>
   <si>
-    <t>Conservation</t>
-  </si>
-  <si>
     <t>https://greenjobs.greenjobsearch.org/jobs/technical-services-manager/</t>
   </si>
   <si>
+    <t>Academic Advisement Assistant/College Assistant</t>
+  </si>
+  <si>
+    <t>CUNY School of Professional Studies</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f28f2fef9554b659cceab08d2a087dc-academic-advisement-assistantcollege-assistant-cuny-school-of-professional-studies-new-york</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -751,6 +802,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/cc0dd51d5b6242f78002f1b7468b1731-administrative-assistant-wafa-house-inc-woodland-park</t>
   </si>
   <si>
+    <t>Administrative Specialist</t>
+  </si>
+  <si>
+    <t>NewBridges Immigrant Resource Center</t>
+  </si>
+  <si>
+    <t>Harrisonburg, Virginia</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8861638aa37b4340824fa7c2e427899a-administrative-specialist-newbridges-immigrant-resource-center-harrisonburg</t>
+  </si>
+  <si>
     <t>Administrative Specialist - Personnel and Human Resources</t>
   </si>
   <si>
@@ -787,6 +856,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/df2a265b80bf4ac78d31d28c9f1a14ca-advancement-assistant-richmond-symphony-richmond</t>
   </si>
   <si>
+    <t>Advancement Officer</t>
+  </si>
+  <si>
+    <t>Youth Enrichment Services (YES)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdb8141e93484e7ab3246b46e1654f26-advancement-officer-youth-enrichment-services-yes-boston</t>
+  </si>
+  <si>
     <t>Assistant Controller</t>
   </si>
   <si>
@@ -850,9 +934,6 @@
     <t>New Cairo City, Cairo Governorate, EG</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Job Workplace</t>
   </si>
   <si>
@@ -898,9 +979,6 @@
     <t>Youth Justice Network</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 60000.00/year</t>
   </si>
   <si>
@@ -910,6 +988,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/c7ca05b9983e425d82c3a9d72bae40a2-career-specialist-youth-justice-network-new-york</t>
   </si>
   <si>
+    <t>Chief Executive Officer (CEO)</t>
+  </si>
+  <si>
+    <t>MaxAbilities of York County</t>
+  </si>
+  <si>
+    <t>York, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 127000.00 - 159000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5835f4c3aa9e4e8d953d67ca8a13db87-chief-executive-officer-ceo-maxabilities-of-york-county-york</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer &amp; Executive Producer</t>
+  </si>
+  <si>
+    <t>Gay Men's Chorus of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff15a27e39764692a6a5882e7d41e95b-chief-executive-officer-executive-producer-gay-mens-chorus-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Clinical Nurse Manager</t>
   </si>
   <si>
@@ -985,6 +1099,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/48a325a80fef49f2a51313bd0d25193f-community-education-outreach-manager-parkinsons-foundation-miami</t>
   </si>
   <si>
+    <t>Community Engagement Associate - Mandarin</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85b3eb53122344a89e32e0884dea599a-community-engagement-associate-mandarin-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
     <t>Community Engagement Coordinator (Part-Time, Yonkers Outreach)</t>
   </si>
   <si>
@@ -994,9 +1126,6 @@
     <t>Yonkers, New York</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 20.00 - 20.00/hour</t>
   </si>
   <si>
@@ -1042,6 +1171,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/db7adcc7381d426492ba123a9a922513-deaf-ministry-coordinator-archdiocese-of-washington-archdiocese-of-washington-washington</t>
   </si>
   <si>
+    <t>Deputy Director of Advancement</t>
+  </si>
+  <si>
+    <t>Cayton Children's Museum</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 65.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42b59e5b8e144fdc9dc7587d971302ed-deputy-director-of-advancement-cayton-childrens-museum-los-angeles</t>
+  </si>
+  <si>
     <t>Development and Operations Associate</t>
   </si>
   <si>
@@ -1060,6 +1204,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/2467caf419c54a5da9fc0660302b07a1-development-and-operations-associate-tookanytacony-frankford-watershed-partnership-inc-philadelphia</t>
   </si>
   <si>
+    <t>Development Assistant-Midwest Region</t>
+  </si>
+  <si>
+    <t>American Friends of The Hebrew University</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/caaa01576da04fedbe0cfe5bf5227bd9-development-assistant-midwest-region-american-friends-of-the-hebrew-university-new-york</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>National Alliance on Mental Illness of New York City (NAMI-NYC Metro)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/830b1fa9cd1a4eccb681e17c3ef97e0c-development-associate-national-alliance-on-mental-illness-of-new-york-city-nami-nyc-metro-new-york</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77fb5b326be54b37b07db1d5baa754fc-development-associate-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
     <t>Development Coordinator</t>
   </si>
   <si>
@@ -1087,9 +1279,6 @@
     <t>Holyoke, Massachusetts</t>
   </si>
   <si>
-    <t>USD 65000.00 - 75000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Civic Engagement, Conflict Resolution</t>
   </si>
   <si>
@@ -1111,6 +1300,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/36a82832ba364c349f6e19a2093b68cb-development-manager-arcadia-center-for-sustainable-food-and-agriculture-alexandria</t>
   </si>
   <si>
+    <t>Cystic Fibrosis Foundation - Cff.org</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>Health Medicine, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4edee90772d9466a9610f0bb7c0ec3e5-development-manager-cystic-fibrosis-foundation-cfforg-denver</t>
+  </si>
+  <si>
     <t>Digital Media Engineer</t>
   </si>
   <si>
@@ -1153,6 +1354,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/745b8660bd3a492796da4c9401237931-director-of-early-childhood-education-united-south-end-settlements-boston</t>
   </si>
   <si>
+    <t>Director of Individual Giving</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 125500.00 - 141500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47ec2d2a72e143c685610369e86e0740-director-of-individual-giving-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Caramoor Center for Music and the Arts, Inc.</t>
+  </si>
+  <si>
+    <t>Katonah, New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afaaaf010449484b9377e802df67e624-director-of-individual-giving-caramoor-center-for-music-and-the-arts-inc-katonah</t>
+  </si>
+  <si>
     <t>DIRECTOR OF LEGAL SERVICES</t>
   </si>
   <si>
@@ -1201,6 +1432,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/4b153a563ef04452ae3dca3ed16cbfd5-director-of-political-affairs-american-speech-language-hearing-association-rockville</t>
   </si>
   <si>
+    <t>Director of Strategic Revenue &amp; Growth</t>
+  </si>
+  <si>
+    <t>People's Light &amp; Theatre</t>
+  </si>
+  <si>
+    <t>Malvern, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dadafae234f3438ea1b27ef616903073-director-of-strategic-revenue-growth-peoples-light-theatre-malvern</t>
+  </si>
+  <si>
+    <t>Director, School Partnership &amp; Coaching Western Washington</t>
+  </si>
+  <si>
+    <t>College Success Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 114698.00 - 172042.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd063be59d294c63b873f5ba68e7c225-director-school-partnership-coaching-western-washington-college-success-foundation-bellevue</t>
+  </si>
+  <si>
     <t>Distribution Center &amp; Warehouse Associate- Full-Time and Part-Time Positions Available</t>
   </si>
   <si>
@@ -1273,6 +1540,24 @@
     <t>https://www.idealist.org/en/government-job/a13d46e1dd5b4ff3b3e43beb39a7dccc-engineering-manager-first-5-alameda-county-alameda</t>
   </si>
   <si>
+    <t>Evaluation &amp; Data Specialist</t>
+  </si>
+  <si>
+    <t>Respect Together</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55286.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/404bafdc2a4a4b6a938eb91cceea66c4-evaluation-data-specialist-respect-together-harrisburg</t>
+  </si>
+  <si>
     <t>Executive Assistant to the Director &amp; CEO</t>
   </si>
   <si>
@@ -1282,6 +1567,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7bdbe7c7161c44ba85a947e34f7fb5be-executive-assistant-to-the-director-ceo-the-newark-museum-of-art-newark</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>The Climate Center</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Policy, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c039b66aa47455f8e59077401a8f003-executive-director-the-climate-center-sacramento</t>
+  </si>
+  <si>
     <t>Executive Director - Local Corps Collective</t>
   </si>
   <si>
@@ -1309,6 +1609,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b06be3f8674847ec9a5eaf6b5522cd1b-executive-transformation-and-strategy-officer-heifer-international-little-rock</t>
   </si>
   <si>
+    <t>File Clerk</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Forest Hills, NY</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c263333bd2a4141bd7de1767cae156b-file-clerk-brooklyn-defender-services-forest-hills</t>
+  </si>
+  <si>
     <t>Financial Analyst</t>
   </si>
   <si>
@@ -1345,12 +1663,6 @@
     <t>Housing Triage Attorney</t>
   </si>
   <si>
-    <t>Open Door Legal</t>
-  </si>
-  <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 83500.00 - 99500.00/year</t>
   </si>
   <si>
@@ -1369,6 +1681,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/82bfeb70747f4833a739a31a939d1632-immigration-staff-attorney-cabrini-immigrant-services-of-nyc-new-york</t>
   </si>
   <si>
+    <t>Job Title: Fundraiser / Development Specialist</t>
+  </si>
+  <si>
+    <t>New Day Community Development Corporation</t>
+  </si>
+  <si>
+    <t>Rye Brook, New York</t>
+  </si>
+  <si>
+    <t>USD 4000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34de3ea84ea64d2bbf85572468a35407-job-title-fundraiser-development-specialist-new-day-community-development-corporation-rye-brook</t>
+  </si>
+  <si>
+    <t>Leave and Accommodations Administrator</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bcf2299edcc44f0be815bd508e6c200-leave-and-accommodations-administrator-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
     <t>Legal Assistant/Screener</t>
   </si>
   <si>
@@ -1384,21 +1723,33 @@
     <t>https://www.idealist.org/en/job/b61912c129274189a6194a74e4e41cc3-legal-assistantscreener-pisgah-legal-services-asheville</t>
   </si>
   <si>
+    <t>Litigation and Economic Justice Triage Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c790fcabad98493d9099c29642625356-litigation-and-economic-justice-triage-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>Major Gifts Officer</t>
   </si>
   <si>
     <t>Village Health Works</t>
   </si>
   <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Education</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/6afc56df11c54e3783497959fb10bdf0-major-gifts-officer-village-health-works-new-york</t>
   </si>
   <si>
+    <t>Providence Public Library</t>
+  </si>
+  <si>
+    <t>Providence, RI</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90ff96f0241f4002af61345727606c0d-major-gifts-officer-providence-public-library-providence</t>
+  </si>
+  <si>
     <t>Manager, School Partnerships</t>
   </si>
   <si>
@@ -1441,6 +1792,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9ecde76c9a5b496fbf8f3587d9d92e3e-managing-family-law-attorney-open-door-legal-san-francisco</t>
   </si>
   <si>
+    <t>Marketing &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Unravel</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4d772bab1bb4f4a9833b0df65da8945-marketing-communications-manager-unravel-gilroy</t>
+  </si>
+  <si>
     <t>Membership Assistant</t>
   </si>
   <si>
@@ -1477,6 +1843,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/281dd3714c6141a484a01c56b0a127b2-membership-engagement-manager-american-academy-of-arts-and-sciences-cambridge</t>
   </si>
   <si>
+    <t>Mitigation Specialist, Criminal Trials Staten Island</t>
+  </si>
+  <si>
+    <t>The Legal Aid Society - New York City</t>
+  </si>
+  <si>
+    <t>USD 83631.00 - 125627.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/468663ae90f84722be3f684cb3ac18ba-mitigation-specialist-criminal-trials-staten-island-the-legal-aid-society-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Mitigation Specialist, Exploitation Intervention Project</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78e6d994fd8e45c3bda4019d0b7b584e-mitigation-specialist-exploitation-intervention-project-the-legal-aid-society-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>New York State School Food Operations Specialist</t>
+  </si>
+  <si>
+    <t>Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 66027.00 - 89215.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4f67d0e2311743a7a0169b52a43c9682-new-york-state-school-food-operations-specialist-chef-ann-foundation-monticello</t>
+  </si>
+  <si>
     <t>Nutrition Program Manager</t>
   </si>
   <si>
@@ -1489,6 +1894,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0816237f20514b84a2f7211c9979ee80-nutrition-program-manager-iona-senior-services-washington</t>
   </si>
   <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>Student Immigrant Movement</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6ba65d728044d85b777a8bd6d807e4e-organizing-director-student-immigrant-movement-boston</t>
+  </si>
+  <si>
     <t>Part-time Accountant</t>
   </si>
   <si>
@@ -1501,6 +1921,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/1e2a2c6acaf548d980177c79cccd3eb5-part-time-accountant-lev-foundation-seattle</t>
   </si>
   <si>
+    <t>People, Finance and Operations Manager</t>
+  </si>
+  <si>
+    <t>Forward Together</t>
+  </si>
+  <si>
+    <t>USD 81807.00 - 87387.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef3a17dabf884aaa9a5a85577848660e-people-finance-and-operations-manager-forward-together-oakland</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>Food &amp; Friends</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb102a67a2ea4e778432f6c416584da1-philanthropy-officer-food-friends-washington</t>
+  </si>
+  <si>
     <t>Post-baccalaureate/Post-doctoral Bioethics Fellowship at the NIH</t>
   </si>
   <si>
@@ -1564,6 +2014,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/be031c6e10ea434d9c07ac4b0903a306-program-assistant-new-york-health-foundation-new-york</t>
   </si>
   <si>
+    <t>Program Coordinator - Therapeutic Playroom</t>
+  </si>
+  <si>
+    <t>Safe &amp; Sound</t>
+  </si>
+  <si>
+    <t>USD 32.77/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/526156b4ff8c4e01b5b33584723b26f0-program-coordinator-therapeutic-playroom-safe-sound-san-francisco</t>
+  </si>
+  <si>
+    <t>Program Evaluation + Administration Coordinator</t>
+  </si>
+  <si>
+    <t>COMMUNITIES TOGETHER INC (CTI)</t>
+  </si>
+  <si>
+    <t>USD 60050.00 - 64500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f23efb8b25949f6bbf8c93ab228e7cd-program-evaluation-administration-coordinator-communities-together-inc-cti-bethesda</t>
+  </si>
+  <si>
+    <t>Project Management Lead</t>
+  </si>
+  <si>
+    <t>Coleridge Initiative</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Research Social Science, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/556dc29207b147fcb2feb0842a113308-project-management-lead-coleridge-initiative-washington</t>
+  </si>
+  <si>
     <t>PUBLIC DEFENDER CLIENT ADVOCATE</t>
   </si>
   <si>
@@ -1582,6 +2077,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ddd04010d7e403698a036177ebe6d5e-public-defender-client-advocate-partners-for-justice-chesterfield</t>
   </si>
   <si>
+    <t>PUBLIC DEFENDER CLIENT ADVOCATE - Chesterfield, VA on-site</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ddd04010d7e403698a036177ebe6d5e-public-defender-client-advocate-chesterfield-va-on-site-partners-for-justice-chesterfield</t>
+  </si>
+  <si>
+    <t>PUBLIC DEFENDER CLIENT ADVOCATE - Yreka, California (on-site)</t>
+  </si>
+  <si>
+    <t>Yreka, California</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 61000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/303eec1525454dc1a78384cde2e8f8e3-public-defender-client-advocate-yreka-california-on-site-partners-for-justice-yreka</t>
+  </si>
+  <si>
     <t>Recruitment Specialist</t>
   </si>
   <si>
@@ -1648,6 +2161,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/2b4d55f22fd6471585ac588baf948f61-senior-civil-litigation-attorney-open-door-legal-san-francisco</t>
   </si>
   <si>
+    <t>Senior Communications Manager</t>
+  </si>
+  <si>
+    <t>Earth Island Institute</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 120863.00 - 120863.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24d3254a2cdc4d118a19115c540f41c5-senior-communications-manager-earth-island-institute-berkeley</t>
+  </si>
+  <si>
+    <t>Senior Director of Development &amp; Major Gifts</t>
+  </si>
+  <si>
+    <t>Island Senior Resources</t>
+  </si>
+  <si>
+    <t>Langley, Washington</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c55ebe21ce0d4d758776daae1882e087-senior-director-of-development-major-gifts-island-senior-resources-langley</t>
+  </si>
+  <si>
     <t>Senior Eviction Defense (UD) Housing Attorney</t>
   </si>
   <si>
@@ -1678,6 +2224,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/e0ce69030b574787b92b120f28ea2f06-senior-probate-attorney-open-door-legal-san-francisco</t>
   </si>
   <si>
+    <t>Senior Product Manager</t>
+  </si>
+  <si>
+    <t>Rivet Education</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/4ee73007316a46ee9a2c3173e9792b70-senior-product-manager-rivet-education-saint-francisville</t>
+  </si>
+  <si>
+    <t>Senior Program Manager, Government Partnerships</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43ae9a7c36f649f3b0b73be8c0987218-senior-program-manager-government-partnerships-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Strategist, Federal Advocacy, Advocacy &amp; Partnerships</t>
   </si>
   <si>
@@ -1723,15 +2296,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5704bf4031554c78a75bef4226c81200-special-assistant-guardrails-action-washington</t>
   </si>
   <si>
+    <t>Special Assistant, Executive Office</t>
+  </si>
+  <si>
+    <t>Orbis International</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0de2c3e642b14ba29c9204c24cc4064b-special-assistant-executive-office-orbis-international-new-york</t>
+  </si>
+  <si>
     <t>Specialist, Institutional Partnerships</t>
   </si>
   <si>
     <t>Capital Area Food Bank</t>
   </si>
   <si>
-    <t>Washington, DC</t>
-  </si>
-  <si>
     <t>USD 27.29 - 33.35/hour</t>
   </si>
   <si>
@@ -1759,9 +2338,6 @@
     <t>Coalition to Abolish Slavery &amp; Trafficking (CAST)</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -1822,6 +2398,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/757740555ee146b9ab78c72769a082b5-supervising-or-staff-attorney-women-survivors-program-illinois-prison-project-chicago</t>
   </si>
   <si>
+    <t>Supportive Housing Coordinator - Rapid Re-Housing</t>
+  </si>
+  <si>
+    <t>Homeless Services Network of Central Florida</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5170885076f4da39f7b3cb0e30a3db9-supportive-housing-coordinator-rapid-re-housing-homeless-services-network-of-central-florida-orlando</t>
+  </si>
+  <si>
+    <t>Teaching Artist</t>
+  </si>
+  <si>
+    <t>The Shining Stars Project, Inc.</t>
+  </si>
+  <si>
+    <t>Manteca, California</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c857a35b1ff41f5b6315f51b050d326-teaching-artist-the-shining-stars-project-inc-manteca</t>
+  </si>
+  <si>
     <t>Tech Lead — Backend &amp; Platform</t>
   </si>
   <si>
@@ -1843,6 +2455,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/685c9565cfa34a16bb9f1e189115d2eb-technical-advisor-international-business-economic-development-the-salvation-army-national-headquarters-alexandria</t>
   </si>
   <si>
+    <t>Sequoia Ecological Consulting, Inc.</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3c279a37008342d0bde415a6a1e30e09-technical-services-manager-sequoia-ecological-consulting-inc-walnut-creek</t>
+  </si>
+  <si>
     <t>Technology Operations Director</t>
   </si>
   <si>
@@ -1895,6 +2516,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d82a2ff7f2814bfaa44ba5430b5820ce-victim-services-coordinator-victim-support-services-everett</t>
+  </si>
+  <si>
+    <t>Volunteer Program Coordinator</t>
+  </si>
+  <si>
+    <t>Travelers Aid International</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation, Civic Engagement, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08748d34563b4c89bba8d6409120ee64-volunteer-program-coordinator-travelers-aid-international-philadelphia</t>
   </si>
   <si>
     <t>Web Developer &amp; Digital Applications Specialist</t>
@@ -2851,13 +3487,16 @@
       <c r="F23" t="s">
         <v>121</v>
       </c>
+      <c r="G23" t="s">
+        <v>122</v>
+      </c>
       <c r="H23" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
         <v>49</v>
@@ -2875,84 +3514,84 @@
         <v>52</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F27" t="s">
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
         <v>104</v>
@@ -2961,358 +3600,358 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F35" t="s">
         <v>94</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D37" t="s">
         <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
         <v>94</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F38" t="s">
         <v>116</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F39" t="s">
         <v>116</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D42" t="s">
         <v>37</v>
       </c>
       <c r="E42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F43" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3368,7 +4007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3409,31 +4048,82 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" t="s">
         <v>229</v>
       </c>
-      <c r="F2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" t="s">
         <v>231</v>
+      </c>
+      <c r="G3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3442,7 +4132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3483,2026 +4173,3015 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" t="s">
         <v>252</v>
       </c>
-      <c r="C5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" t="s">
-        <v>241</v>
-      </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E6" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F6" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="F8" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="F10" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B11" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F11" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" t="s">
         <v>300</v>
       </c>
-      <c r="D13" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" t="s">
-        <v>301</v>
-      </c>
       <c r="F13" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B14" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C14" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="E14" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="F14" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="F15" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C16" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E16" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="F16" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C17" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E17" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="F17" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D18" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
       <c r="E18" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F18" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C19" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E19" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="F19" t="s">
-        <v>278</v>
+        <v>345</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B20" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C20" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B21" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C21" t="s">
-        <v>300</v>
+        <v>353</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E21" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="F21" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B22" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="C22" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E22" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="F22" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B23" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="C23" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="F23" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="B24" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="C24" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E24" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="F24" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="B25" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C25" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E25" t="s">
-        <v>357</v>
+        <v>246</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>246</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B26" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E26" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="F26" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B27" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C27" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E27" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="F27" t="s">
-        <v>278</v>
+        <v>383</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="B28" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="C28" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E28" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="F28" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="B29" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E29" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F29" t="s">
-        <v>296</v>
+        <v>394</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B30" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C30" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E30" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="F30" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="B31" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="C31" t="s">
-        <v>387</v>
+        <v>244</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E31" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="F31" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B32" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>408</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E32" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="F32" t="s">
-        <v>278</v>
+        <v>410</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="B33" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="C33" t="s">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E33" t="s">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="F33" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="B34" t="s">
-        <v>310</v>
+        <v>415</v>
       </c>
       <c r="C34" t="s">
-        <v>315</v>
+        <v>416</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E34" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="F34" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="B35" t="s">
-        <v>310</v>
+        <v>419</v>
       </c>
       <c r="C35" t="s">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E35" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F35" t="s">
-        <v>313</v>
+        <v>421</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="B36" t="s">
-        <v>310</v>
+        <v>424</v>
       </c>
       <c r="C36" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E36" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="F36" t="s">
-        <v>313</v>
+        <v>426</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="B37" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C37" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="D37" t="s">
-        <v>406</v>
+        <v>258</v>
       </c>
       <c r="E37" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="F37" t="s">
-        <v>278</v>
+        <v>430</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="B38" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C38" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E38" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="F38" t="s">
-        <v>411</v>
+        <v>246</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="B39" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C39" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E39" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="F39" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="B40" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C40" t="s">
-        <v>352</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E40" t="s">
-        <v>357</v>
+        <v>444</v>
       </c>
       <c r="F40" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="B41" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>448</v>
       </c>
       <c r="D41" t="s">
-        <v>406</v>
+        <v>258</v>
       </c>
       <c r="E41" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F41" t="s">
-        <v>425</v>
+        <v>246</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B42" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C42" t="s">
-        <v>306</v>
+        <v>452</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E42" t="s">
-        <v>278</v>
+        <v>453</v>
       </c>
       <c r="F42" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="C43" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E43" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="F43" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B44" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="C44" t="s">
-        <v>306</v>
+        <v>464</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="F44" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E45" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="F45" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="B46" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="C46" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="D46" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E46" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F46" t="s">
-        <v>278</v>
+        <v>476</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="B47" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>480</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E47" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="F47" t="s">
-        <v>278</v>
+        <v>482</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="B48" t="s">
-        <v>452</v>
+        <v>348</v>
       </c>
       <c r="C48" t="s">
-        <v>453</v>
+        <v>349</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E48" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="F48" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="B49" t="s">
-        <v>457</v>
+        <v>348</v>
       </c>
       <c r="C49" t="s">
-        <v>458</v>
+        <v>353</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E49" t="s">
-        <v>301</v>
+        <v>485</v>
       </c>
       <c r="F49" t="s">
-        <v>459</v>
+        <v>351</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="B50" t="s">
-        <v>462</v>
+        <v>348</v>
       </c>
       <c r="C50" t="s">
-        <v>463</v>
+        <v>353</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E50" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="F50" t="s">
-        <v>465</v>
+        <v>351</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s">
-        <v>468</v>
+        <v>348</v>
       </c>
       <c r="C51" t="s">
-        <v>469</v>
+        <v>349</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E51" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="F51" t="s">
-        <v>471</v>
+        <v>351</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="B52" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="C52" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>495</v>
       </c>
       <c r="E52" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="F52" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="B53" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="C53" t="s">
-        <v>477</v>
+        <v>338</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E53" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="F53" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="C54" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E54" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="F54" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="C55" t="s">
-        <v>300</v>
+        <v>510</v>
       </c>
       <c r="D55" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E55" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="F55" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="B56" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="C56" t="s">
-        <v>493</v>
+        <v>416</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E56" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="F56" t="s">
-        <v>471</v>
+        <v>278</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="B57" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="C57" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="D57" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="E57" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="F57" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="C58" t="s">
-        <v>502</v>
+        <v>222</v>
       </c>
       <c r="D58" t="s">
-        <v>241</v>
+        <v>495</v>
       </c>
       <c r="E58" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="F58" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="D59" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E59" t="s">
-        <v>508</v>
+        <v>246</v>
       </c>
       <c r="F59" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="B60" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="C60" t="s">
-        <v>294</v>
+        <v>533</v>
       </c>
       <c r="D60" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E60" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="F60" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="C61" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="D61" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E61" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="F61" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="B62" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="C62" t="s">
-        <v>524</v>
+        <v>344</v>
       </c>
       <c r="D62" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E62" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F62" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="B63" t="s">
-        <v>529</v>
+        <v>286</v>
       </c>
       <c r="C63" t="s">
-        <v>530</v>
+        <v>287</v>
       </c>
       <c r="D63" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E63" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="F63" t="s">
-        <v>532</v>
+        <v>289</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="B64" t="s">
-        <v>535</v>
+        <v>447</v>
       </c>
       <c r="C64" t="s">
-        <v>352</v>
+        <v>448</v>
       </c>
       <c r="D64" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E64" t="s">
-        <v>320</v>
+        <v>549</v>
       </c>
       <c r="F64" t="s">
-        <v>536</v>
+        <v>246</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="B65" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="C65" t="s">
-        <v>444</v>
+        <v>244</v>
       </c>
       <c r="D65" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E65" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="F65" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="B66" t="s">
-        <v>443</v>
+        <v>556</v>
       </c>
       <c r="C66" t="s">
-        <v>444</v>
+        <v>557</v>
       </c>
       <c r="D66" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E66" t="s">
-        <v>278</v>
+        <v>558</v>
       </c>
       <c r="F66" t="s">
-        <v>278</v>
+        <v>559</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s">
-        <v>443</v>
+        <v>298</v>
       </c>
       <c r="C67" t="s">
-        <v>444</v>
+        <v>244</v>
       </c>
       <c r="D67" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E67" t="s">
-        <v>278</v>
+        <v>562</v>
       </c>
       <c r="F67" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="B68" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="C68" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E68" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F68" t="s">
-        <v>550</v>
+        <v>246</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="B69" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C69" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D69" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E69" t="s">
-        <v>278</v>
+        <v>549</v>
       </c>
       <c r="F69" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
+        <v>398</v>
       </c>
       <c r="D70" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E70" t="s">
-        <v>556</v>
+        <v>339</v>
       </c>
       <c r="F70" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B71" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="C71" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="D71" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E71" t="s">
-        <v>562</v>
+        <v>288</v>
       </c>
       <c r="F71" t="s">
-        <v>563</v>
+        <v>254</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="B72" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="C72" t="s">
-        <v>306</v>
+        <v>580</v>
       </c>
       <c r="D72" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E72" t="s">
-        <v>260</v>
+        <v>581</v>
       </c>
       <c r="F72" t="s">
-        <v>278</v>
+        <v>582</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="B73" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="C73" t="s">
-        <v>306</v>
+        <v>586</v>
       </c>
       <c r="D73" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E73" t="s">
-        <v>260</v>
+        <v>587</v>
       </c>
       <c r="F73" t="s">
-        <v>278</v>
+        <v>588</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="B74" t="s">
-        <v>570</v>
+        <v>447</v>
       </c>
       <c r="C74" t="s">
-        <v>571</v>
+        <v>448</v>
       </c>
       <c r="D74" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E74" t="s">
-        <v>572</v>
+        <v>246</v>
       </c>
       <c r="F74" t="s">
-        <v>573</v>
+        <v>246</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="B75" t="s">
-        <v>386</v>
+        <v>593</v>
       </c>
       <c r="C75" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="D75" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E75" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="F75" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="B76" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="C76" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="D76" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E76" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="F76" t="s">
-        <v>278</v>
+        <v>601</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="B77" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="C77" t="s">
-        <v>294</v>
+        <v>605</v>
       </c>
       <c r="D77" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="F77" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="B78" t="s">
-        <v>380</v>
+        <v>610</v>
       </c>
       <c r="C78" t="s">
-        <v>589</v>
+        <v>244</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E78" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="F78" t="s">
-        <v>383</v>
+        <v>612</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="B79" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="C79" t="s">
-        <v>444</v>
+        <v>244</v>
       </c>
       <c r="D79" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="E79" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="F79" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="B80" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="C80" t="s">
-        <v>469</v>
+        <v>619</v>
       </c>
       <c r="D80" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E80" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="F80" t="s">
-        <v>600</v>
+        <v>246</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="B81" t="s">
-        <v>603</v>
+        <v>337</v>
       </c>
       <c r="C81" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E81" t="s">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="F81" t="s">
-        <v>279</v>
+        <v>624</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="B82" t="s">
-        <v>246</v>
+        <v>627</v>
       </c>
       <c r="C82" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="D82" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E82" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="F82" t="s">
-        <v>249</v>
+        <v>629</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="B83" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="C83" t="s">
-        <v>306</v>
+        <v>633</v>
       </c>
       <c r="D83" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E83" t="s">
-        <v>611</v>
+        <v>350</v>
       </c>
       <c r="F83" t="s">
-        <v>612</v>
+        <v>588</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="B84" t="s">
-        <v>443</v>
+        <v>636</v>
       </c>
       <c r="C84" t="s">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="D84" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E84" t="s">
-        <v>278</v>
+        <v>637</v>
       </c>
       <c r="F84" t="s">
-        <v>278</v>
+        <v>638</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="B85" t="s">
-        <v>443</v>
+        <v>641</v>
       </c>
       <c r="C85" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="D85" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E85" t="s">
-        <v>278</v>
+        <v>642</v>
       </c>
       <c r="F85" t="s">
-        <v>278</v>
+        <v>643</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>617</v>
+        <v>644</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="B86" t="s">
-        <v>386</v>
+        <v>646</v>
       </c>
       <c r="C86" t="s">
-        <v>387</v>
+        <v>647</v>
       </c>
       <c r="D86" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="E86" t="s">
-        <v>619</v>
+        <v>246</v>
       </c>
       <c r="F86" t="s">
-        <v>577</v>
+        <v>648</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="B87" t="s">
-        <v>622</v>
+        <v>651</v>
       </c>
       <c r="C87" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="D87" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="E87" t="s">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="F87" t="s">
-        <v>625</v>
+        <v>654</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="B88" t="s">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="C88" t="s">
-        <v>629</v>
+        <v>344</v>
       </c>
       <c r="D88" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E88" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="F88" t="s">
-        <v>504</v>
+        <v>659</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>631</v>
+        <v>660</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="B89" t="s">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="C89" t="s">
-        <v>634</v>
+        <v>244</v>
       </c>
       <c r="D89" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E89" t="s">
-        <v>513</v>
+        <v>663</v>
       </c>
       <c r="F89" t="s">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>636</v>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>666</v>
+      </c>
+      <c r="B90" t="s">
+        <v>667</v>
+      </c>
+      <c r="C90" t="s">
+        <v>448</v>
+      </c>
+      <c r="D90" t="s">
+        <v>258</v>
+      </c>
+      <c r="E90" t="s">
+        <v>668</v>
+      </c>
+      <c r="F90" t="s">
+        <v>669</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>671</v>
+      </c>
+      <c r="B91" t="s">
+        <v>672</v>
+      </c>
+      <c r="C91" t="s">
+        <v>647</v>
+      </c>
+      <c r="D91" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" t="s">
+        <v>673</v>
+      </c>
+      <c r="F91" t="s">
+        <v>674</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>676</v>
+      </c>
+      <c r="B92" t="s">
+        <v>677</v>
+      </c>
+      <c r="C92" t="s">
+        <v>344</v>
+      </c>
+      <c r="D92" t="s">
+        <v>258</v>
+      </c>
+      <c r="E92" t="s">
+        <v>678</v>
+      </c>
+      <c r="F92" t="s">
+        <v>679</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>681</v>
+      </c>
+      <c r="B93" t="s">
+        <v>682</v>
+      </c>
+      <c r="C93" t="s">
+        <v>683</v>
+      </c>
+      <c r="D93" t="s">
+        <v>258</v>
+      </c>
+      <c r="E93" t="s">
+        <v>684</v>
+      </c>
+      <c r="F93" t="s">
+        <v>685</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>687</v>
+      </c>
+      <c r="B94" t="s">
+        <v>682</v>
+      </c>
+      <c r="C94" t="s">
+        <v>683</v>
+      </c>
+      <c r="D94" t="s">
+        <v>258</v>
+      </c>
+      <c r="E94" t="s">
+        <v>684</v>
+      </c>
+      <c r="F94" t="s">
+        <v>685</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>689</v>
+      </c>
+      <c r="B95" t="s">
+        <v>682</v>
+      </c>
+      <c r="C95" t="s">
+        <v>690</v>
+      </c>
+      <c r="D95" t="s">
+        <v>258</v>
+      </c>
+      <c r="E95" t="s">
+        <v>691</v>
+      </c>
+      <c r="F95" t="s">
+        <v>685</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>693</v>
+      </c>
+      <c r="B96" t="s">
+        <v>694</v>
+      </c>
+      <c r="C96" t="s">
+        <v>695</v>
+      </c>
+      <c r="D96" t="s">
+        <v>258</v>
+      </c>
+      <c r="E96" t="s">
+        <v>696</v>
+      </c>
+      <c r="F96" t="s">
+        <v>697</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>699</v>
+      </c>
+      <c r="B97" t="s">
+        <v>700</v>
+      </c>
+      <c r="C97" t="s">
+        <v>701</v>
+      </c>
+      <c r="D97" t="s">
+        <v>258</v>
+      </c>
+      <c r="E97" t="s">
+        <v>702</v>
+      </c>
+      <c r="F97" t="s">
+        <v>703</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>705</v>
+      </c>
+      <c r="B98" t="s">
+        <v>706</v>
+      </c>
+      <c r="C98" t="s">
+        <v>416</v>
+      </c>
+      <c r="D98" t="s">
+        <v>258</v>
+      </c>
+      <c r="E98" t="s">
+        <v>358</v>
+      </c>
+      <c r="F98" t="s">
+        <v>707</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>709</v>
+      </c>
+      <c r="B99" t="s">
+        <v>710</v>
+      </c>
+      <c r="C99" t="s">
+        <v>448</v>
+      </c>
+      <c r="D99" t="s">
+        <v>258</v>
+      </c>
+      <c r="E99" t="s">
+        <v>711</v>
+      </c>
+      <c r="F99" t="s">
+        <v>254</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>713</v>
+      </c>
+      <c r="B100" t="s">
+        <v>447</v>
+      </c>
+      <c r="C100" t="s">
+        <v>448</v>
+      </c>
+      <c r="D100" t="s">
+        <v>258</v>
+      </c>
+      <c r="E100" t="s">
+        <v>246</v>
+      </c>
+      <c r="F100" t="s">
+        <v>246</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>715</v>
+      </c>
+      <c r="B101" t="s">
+        <v>716</v>
+      </c>
+      <c r="C101" t="s">
+        <v>717</v>
+      </c>
+      <c r="D101" t="s">
+        <v>258</v>
+      </c>
+      <c r="E101" t="s">
+        <v>718</v>
+      </c>
+      <c r="F101" t="s">
+        <v>719</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>721</v>
+      </c>
+      <c r="B102" t="s">
+        <v>722</v>
+      </c>
+      <c r="C102" t="s">
+        <v>723</v>
+      </c>
+      <c r="D102" t="s">
+        <v>258</v>
+      </c>
+      <c r="E102" t="s">
+        <v>724</v>
+      </c>
+      <c r="F102" t="s">
+        <v>500</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>726</v>
+      </c>
+      <c r="B103" t="s">
+        <v>447</v>
+      </c>
+      <c r="C103" t="s">
+        <v>448</v>
+      </c>
+      <c r="D103" t="s">
+        <v>258</v>
+      </c>
+      <c r="E103" t="s">
+        <v>246</v>
+      </c>
+      <c r="F103" t="s">
+        <v>246</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>728</v>
+      </c>
+      <c r="B104" t="s">
+        <v>729</v>
+      </c>
+      <c r="C104" t="s">
+        <v>730</v>
+      </c>
+      <c r="D104" t="s">
+        <v>258</v>
+      </c>
+      <c r="E104" t="s">
+        <v>731</v>
+      </c>
+      <c r="F104" t="s">
+        <v>732</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>734</v>
+      </c>
+      <c r="B105" t="s">
+        <v>447</v>
+      </c>
+      <c r="C105" t="s">
+        <v>448</v>
+      </c>
+      <c r="D105" t="s">
+        <v>258</v>
+      </c>
+      <c r="E105" t="s">
+        <v>246</v>
+      </c>
+      <c r="F105" t="s">
+        <v>246</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>736</v>
+      </c>
+      <c r="B106" t="s">
+        <v>737</v>
+      </c>
+      <c r="C106" t="s">
+        <v>344</v>
+      </c>
+      <c r="D106" t="s">
+        <v>258</v>
+      </c>
+      <c r="E106" t="s">
+        <v>738</v>
+      </c>
+      <c r="F106" t="s">
+        <v>247</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>740</v>
+      </c>
+      <c r="B107" t="s">
+        <v>741</v>
+      </c>
+      <c r="C107" t="s">
+        <v>332</v>
+      </c>
+      <c r="D107" t="s">
+        <v>495</v>
+      </c>
+      <c r="E107" t="s">
+        <v>742</v>
+      </c>
+      <c r="F107" t="s">
+        <v>743</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>745</v>
+      </c>
+      <c r="B108" t="s">
+        <v>746</v>
+      </c>
+      <c r="C108" t="s">
+        <v>338</v>
+      </c>
+      <c r="D108" t="s">
+        <v>258</v>
+      </c>
+      <c r="E108" t="s">
+        <v>747</v>
+      </c>
+      <c r="F108" t="s">
+        <v>748</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>750</v>
+      </c>
+      <c r="B109" t="s">
+        <v>751</v>
+      </c>
+      <c r="C109" t="s">
+        <v>752</v>
+      </c>
+      <c r="D109" t="s">
+        <v>258</v>
+      </c>
+      <c r="E109" t="s">
+        <v>753</v>
+      </c>
+      <c r="F109" t="s">
+        <v>754</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>756</v>
+      </c>
+      <c r="B110" t="s">
+        <v>757</v>
+      </c>
+      <c r="C110" t="s">
+        <v>344</v>
+      </c>
+      <c r="D110" t="s">
+        <v>258</v>
+      </c>
+      <c r="E110" t="s">
+        <v>288</v>
+      </c>
+      <c r="F110" t="s">
+        <v>246</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>756</v>
+      </c>
+      <c r="B111" t="s">
+        <v>757</v>
+      </c>
+      <c r="C111" t="s">
+        <v>344</v>
+      </c>
+      <c r="D111" t="s">
+        <v>258</v>
+      </c>
+      <c r="E111" t="s">
+        <v>288</v>
+      </c>
+      <c r="F111" t="s">
+        <v>246</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>760</v>
+      </c>
+      <c r="B112" t="s">
+        <v>761</v>
+      </c>
+      <c r="C112" t="s">
+        <v>344</v>
+      </c>
+      <c r="D112" t="s">
+        <v>258</v>
+      </c>
+      <c r="E112" t="s">
+        <v>288</v>
+      </c>
+      <c r="F112" t="s">
+        <v>246</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>763</v>
+      </c>
+      <c r="B113" t="s">
+        <v>764</v>
+      </c>
+      <c r="C113" t="s">
+        <v>408</v>
+      </c>
+      <c r="D113" t="s">
+        <v>258</v>
+      </c>
+      <c r="E113" t="s">
+        <v>765</v>
+      </c>
+      <c r="F113" t="s">
+        <v>766</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>768</v>
+      </c>
+      <c r="B114" t="s">
+        <v>463</v>
+      </c>
+      <c r="C114" t="s">
+        <v>464</v>
+      </c>
+      <c r="D114" t="s">
+        <v>252</v>
+      </c>
+      <c r="E114" t="s">
+        <v>769</v>
+      </c>
+      <c r="F114" t="s">
+        <v>770</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>772</v>
+      </c>
+      <c r="B115" t="s">
+        <v>773</v>
+      </c>
+      <c r="C115" t="s">
+        <v>332</v>
+      </c>
+      <c r="D115" t="s">
+        <v>258</v>
+      </c>
+      <c r="E115" t="s">
+        <v>774</v>
+      </c>
+      <c r="F115" t="s">
+        <v>246</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>772</v>
+      </c>
+      <c r="B116" t="s">
+        <v>776</v>
+      </c>
+      <c r="C116" t="s">
+        <v>244</v>
+      </c>
+      <c r="D116" t="s">
+        <v>258</v>
+      </c>
+      <c r="E116" t="s">
+        <v>777</v>
+      </c>
+      <c r="F116" t="s">
+        <v>778</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>780</v>
+      </c>
+      <c r="B117" t="s">
+        <v>457</v>
+      </c>
+      <c r="C117" t="s">
+        <v>781</v>
+      </c>
+      <c r="D117" t="s">
+        <v>258</v>
+      </c>
+      <c r="E117" t="s">
+        <v>782</v>
+      </c>
+      <c r="F117" t="s">
+        <v>460</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>784</v>
+      </c>
+      <c r="B118" t="s">
+        <v>785</v>
+      </c>
+      <c r="C118" t="s">
+        <v>448</v>
+      </c>
+      <c r="D118" t="s">
+        <v>315</v>
+      </c>
+      <c r="E118" t="s">
+        <v>786</v>
+      </c>
+      <c r="F118" t="s">
+        <v>787</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>789</v>
+      </c>
+      <c r="B119" t="s">
+        <v>790</v>
+      </c>
+      <c r="C119" t="s">
+        <v>586</v>
+      </c>
+      <c r="D119" t="s">
+        <v>258</v>
+      </c>
+      <c r="E119" t="s">
+        <v>791</v>
+      </c>
+      <c r="F119" t="s">
+        <v>792</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>794</v>
+      </c>
+      <c r="B120" t="s">
+        <v>795</v>
+      </c>
+      <c r="C120" t="s">
+        <v>796</v>
+      </c>
+      <c r="D120" t="s">
+        <v>258</v>
+      </c>
+      <c r="E120" t="s">
+        <v>797</v>
+      </c>
+      <c r="F120" t="s">
+        <v>798</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>800</v>
+      </c>
+      <c r="B121" t="s">
+        <v>801</v>
+      </c>
+      <c r="C121" t="s">
+        <v>802</v>
+      </c>
+      <c r="D121" t="s">
+        <v>258</v>
+      </c>
+      <c r="E121" t="s">
+        <v>803</v>
+      </c>
+      <c r="F121" t="s">
+        <v>804</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>806</v>
+      </c>
+      <c r="B122" t="s">
+        <v>807</v>
+      </c>
+      <c r="C122" t="s">
+        <v>344</v>
+      </c>
+      <c r="D122" t="s">
+        <v>258</v>
+      </c>
+      <c r="E122" t="s">
+        <v>808</v>
+      </c>
+      <c r="F122" t="s">
+        <v>306</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>810</v>
+      </c>
+      <c r="B123" t="s">
+        <v>269</v>
+      </c>
+      <c r="C123" t="s">
+        <v>270</v>
+      </c>
+      <c r="D123" t="s">
+        <v>258</v>
+      </c>
+      <c r="E123" t="s">
+        <v>811</v>
+      </c>
+      <c r="F123" t="s">
+        <v>272</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>237</v>
+      </c>
+      <c r="B124" t="s">
+        <v>813</v>
+      </c>
+      <c r="C124" t="s">
+        <v>344</v>
+      </c>
+      <c r="D124" t="s">
+        <v>258</v>
+      </c>
+      <c r="E124" t="s">
+        <v>459</v>
+      </c>
+      <c r="F124" t="s">
+        <v>814</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>816</v>
+      </c>
+      <c r="B125" t="s">
+        <v>817</v>
+      </c>
+      <c r="C125" t="s">
+        <v>344</v>
+      </c>
+      <c r="D125" t="s">
+        <v>258</v>
+      </c>
+      <c r="E125" t="s">
+        <v>818</v>
+      </c>
+      <c r="F125" t="s">
+        <v>819</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>821</v>
+      </c>
+      <c r="B126" t="s">
+        <v>447</v>
+      </c>
+      <c r="C126" t="s">
+        <v>448</v>
+      </c>
+      <c r="D126" t="s">
+        <v>258</v>
+      </c>
+      <c r="E126" t="s">
+        <v>246</v>
+      </c>
+      <c r="F126" t="s">
+        <v>246</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>823</v>
+      </c>
+      <c r="B127" t="s">
+        <v>447</v>
+      </c>
+      <c r="C127" t="s">
+        <v>448</v>
+      </c>
+      <c r="D127" t="s">
+        <v>258</v>
+      </c>
+      <c r="E127" t="s">
+        <v>246</v>
+      </c>
+      <c r="F127" t="s">
+        <v>246</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>825</v>
+      </c>
+      <c r="B128" t="s">
+        <v>463</v>
+      </c>
+      <c r="C128" t="s">
+        <v>464</v>
+      </c>
+      <c r="D128" t="s">
+        <v>258</v>
+      </c>
+      <c r="E128" t="s">
+        <v>826</v>
+      </c>
+      <c r="F128" t="s">
+        <v>770</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>828</v>
+      </c>
+      <c r="B129" t="s">
+        <v>829</v>
+      </c>
+      <c r="C129" t="s">
+        <v>830</v>
+      </c>
+      <c r="D129" t="s">
+        <v>315</v>
+      </c>
+      <c r="E129" t="s">
+        <v>831</v>
+      </c>
+      <c r="F129" t="s">
+        <v>832</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>834</v>
+      </c>
+      <c r="B130" t="s">
+        <v>835</v>
+      </c>
+      <c r="C130" t="s">
+        <v>392</v>
+      </c>
+      <c r="D130" t="s">
+        <v>258</v>
+      </c>
+      <c r="E130" t="s">
+        <v>836</v>
+      </c>
+      <c r="F130" t="s">
+        <v>837</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>839</v>
+      </c>
+      <c r="B131" t="s">
+        <v>840</v>
+      </c>
+      <c r="C131" t="s">
+        <v>841</v>
+      </c>
+      <c r="D131" t="s">
+        <v>252</v>
+      </c>
+      <c r="E131" t="s">
+        <v>842</v>
+      </c>
+      <c r="F131" t="s">
+        <v>654</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>844</v>
+      </c>
+      <c r="B132" t="s">
+        <v>845</v>
+      </c>
+      <c r="C132" t="s">
+        <v>846</v>
+      </c>
+      <c r="D132" t="s">
+        <v>258</v>
+      </c>
+      <c r="E132" t="s">
+        <v>663</v>
+      </c>
+      <c r="F132" t="s">
+        <v>847</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -5596,6 +7275,49 @@
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
